--- a/source/marked/marked_LTRL Chapter O ver0.xlsx
+++ b/source/marked/marked_LTRL Chapter O ver0.xlsx
@@ -413,117 +413,153 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E552"/>
+  <dimension ref="A1:E573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>【原书截图】</t>
+          <t>【截图序号：33】</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>【截图序号：33】</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr"/>
+          <t>【正文页数：1】</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>【本章分工】</t>
+        </is>
+      </c>
       <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>（拆分：1，Lanx）（机翻：1，Lanx）（人翻：1，Lanx）（第一次润色（按句）：1，Lanx，请先润色其他页数）（第一次校对：？，？）（第二次润色（按意群）：1，Πλατών）（第二次校对：？，？）（第三次润色：3+，Lanx, 前期润色两次即可）（附加评论/修改建议：3，北邙Ælfræd，北邙Ælfræd，ΑΝΘΡΩΠΟ ）（终润（按段落）：？，？）（终校：？，？）（排版/美化：？，？）】</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【正文页数：1】</t>
+          <t>【一级标题原文】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>INTRODUCTION</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【本章分工】</t>
+          <t>【一级标题译文】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>【译者：机翻】</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>（拆分：1，Lanx）（机翻：1，Lanx）（人翻：1，Lanx）（第一次润色（按句）：1，Lanx，请先润色其他页数）（第一次校对：？，？）（第二次润色（按意群）：1，Πλατών）（第二次校对：？，？）（第三次润色：3+，Lanx, 前期润色两次即可）（附加评论/修改建议：3，北邙Ælfræd，北邙Ælfræd，ΑΝΘΡΩΠΟ ）（终润（按段落）：？，？）（终校：？，？）（排版/美化：？，？）】</t>
+          <t>序言</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【以下为书籍内容】</t>
+          <t>【二级标题原文】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Latin Language </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【章节大标题原文】</t>
+          <t>【二级标题译文】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>【译者：机翻】</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>INTRODUCTION</t>
+          <t>拉丁语</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【章节大标题译文】</t>
+          <t>【章节标题译文】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>【译者：机翻】</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>【译者注释】：作为标题，单拉丁语三个字感觉很奇怪】</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>序言</t>
+          <t>拉丁语这门语言</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【章节标题原文】</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>【正文原文】</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>【原文序号：1】</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Latin Language </t>
+          <t>The Latin language belongs to the Indo-European family of languages.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【章节标题译文】</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>【正文译文】</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>【译文序号：1】</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>【译者：机翻】</t>
@@ -532,95 +568,91 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>拉丁语</t>
+          <t>拉丁语属于印欧语系。( the Indo-European family of languages)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【章节标题译文】</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>【译者注：作为标题，单拉丁语三个字感觉很奇怪】</t>
-        </is>
-      </c>
+          <t>【正文原文】</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>【原文序号：2】</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>拉丁语这门语言</t>
+          <t>The name "Indo-European"indicates the geographic area where these languages were originally spoken.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>【截图序号：33】</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>【译文序号：2】</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>【译者：机翻】</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Latin language belongs to the Indo-European family of languages.</t>
+          <t>“印欧</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>【截图序号：33】</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>【译者：机翻】</t>
-        </is>
-      </c>
+          <t>”</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>拉丁语属于印欧语系。( the Indo-European family of languages)</t>
+          <t>一词指明了最初使用这些语言的地理区域</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>【正文页数：1】</t>
+          <t>（地区？）</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>【译者：机翻】</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The name "Indo-European"indicates the geographic area where these languages were originally spoken.</t>
+          <t>The family includes most of the languages spoken in Europe,as well as those spoken as far east as ancient Persia,Afghanistan,and India.</t>
         </is>
       </c>
     </row>
@@ -632,18 +664,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>【正文页数：1】</t>
+          <t>（拆分：1，Lanx）（机翻：1，Lanx）（人翻：1，Lanx）（第一次润色（按句）：1，Lanx，请先润色其他页数）（第一次校对：？，？）（第二次润色（按意群）：1，Πλατών）（第二次校对：？，？）（第三次润色：3+，Lanx, 前期润色两次即可）（附加评论/修改建议：3，北邙Ælfræd，北邙Ælfræd，ΑΝΘΡΩΠΟ ）（终润（按段落）：？，？）（终校：？，？）（排版/美化：？，？）】</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>【译者：机翻】</t>
+          <t>【译者：Lanx】</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>"印欧 "</t>
+          <t>【译文序号：3】</t>
         </is>
       </c>
     </row>
@@ -655,18 +687,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>【本章分工】</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>【译者：机翻】</t>
-        </is>
-      </c>
+          <t>【一级标题原文】</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>一词指明了最初使用这些语言的地理区域</t>
+          <t>【译者：tuche est】</t>
         </is>
       </c>
     </row>
@@ -678,18 +706,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>【本章分工】</t>
+          <t>【一级标题原文】</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>（地区？）</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>The family includes most of the languages spoken in Europe,as well as those spoken as far east as ancient Persia,Afghanistan,and India.</t>
+          <t>该语系不仅包含了大多数在欧洲使用的语言，那些在遥远东方（这没有大写）——古波斯、阿富汗，和印度——使用的语言也囊括其中。</t>
         </is>
       </c>
     </row>
@@ -701,7 +729,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>【本章分工】</t>
+          <t>【一级标题原文】</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -712,7 +740,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>【译者：tuche est】</t>
+          <t>该语系不仅包含了大多数欧洲语言，还囊括了那些东至古波斯、阿富汗和印度的语言</t>
         </is>
       </c>
     </row>
@@ -724,14 +752,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>（拆分：1，Lanx）（机翻：1，Lanx）（人翻：1，Lanx）（第一次润色（按句）：1，Lanx，请先润色其他页数）（第一次校对：？，？）（第二次润色（按意群）：1，Πλατών）（第二次校对：？，？）（第三次润色：3+，Lanx, 前期润色两次即可）（附加评论/修改建议：3，北邙Ælfræd，北邙Ælfræd，ΑΝΘΡΩΠΟ ）（终润（按段落）：？，？）（终校：？，？）（排版/美化：？，？）】</t>
+          <t>INTRODUCTION</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>该语系不仅包含了大多数在欧洲使用的语言，那些在遥远东方（这没有大写）——古波斯、阿富汗，和印度——使用的语言也囊括其中。</t>
+          <t>By the careful comparison of vocabulary,morphology,and syntax,scholars have shown that all these languages have descended from a common ancestor that is called either</t>
         </is>
       </c>
     </row>
@@ -743,18 +771,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>（拆分：1，Lanx）（机翻：1，Lanx）（人翻：1，Lanx）（第一次润色（按句）：1，Lanx，请先润色其他页数）（第一次校对：？，？）（第二次润色（按意群）：1，Πλατών）（第二次校对：？，？）（第三次润色：3+，Lanx, 前期润色两次即可）（附加评论/修改建议：3，北邙Ælfræd，北邙Ælfræd，ΑΝΘΡΩΠΟ ）（终润（按段落）：？，？）（终校：？，？）（排版/美化：？，？）】</t>
+          <t>INTRODUCTION</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>（地区？）</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>该语系不仅包含了大多数欧洲语言，还囊括了那些东至古波斯、阿富汗和印度的语言</t>
+          <t xml:space="preserve"> Indo- European(IE)or Proto-Indo-European(PIE)</t>
         </is>
       </c>
     </row>
@@ -766,7 +794,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>（拆分：1，Lanx）（机翻：1，Lanx）（人翻：1，Lanx）（第一次润色（按句）：1，Lanx，请先润色其他页数）（第一次校对：？，？）（第二次润色（按意群）：1，Πλατών）（第二次校对：？，？）（第三次润色：3+，Lanx, 前期润色两次即可）（附加评论/修改建议：3，北邙Ælfræd，北邙Ælfræd，ΑΝΘΡΩΠΟ ）（终润（按段落）：？，？）（终校：？，？）（排版/美化：？，？）】</t>
+          <t>INTRODUCTION</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -777,7 +805,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>By the careful comparison of vocabulary,morphology,and syntax,scholars have shown that all these languages have descended from a common ancestor that is called either</t>
+          <t>,which was probably spoken some time in the fifth millennium B.c.E.(see figure 1).</t>
         </is>
       </c>
     </row>
@@ -789,14 +817,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>【以下为书籍内容】</t>
+          <t>【一级标题译文】</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Indo- European(IE)or Proto-Indo-European(PIE)</t>
+          <t>通过对词汇、词法，以及句法的详细比较研究，学者们发现所有上述语言都源自一个被称为</t>
         </is>
       </c>
     </row>
@@ -808,18 +836,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>【以下为书籍内容】</t>
+          <t>【一级标题译文】</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>（地区？）</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>,which was probably spoken some time in the fifth millennium B.c.E.(see figure 1).</t>
+          <t>印欧语或原始印欧语</t>
         </is>
       </c>
     </row>
@@ -831,7 +859,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>【以下为书籍内容】</t>
+          <t>【一级标题译文】</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -842,7 +870,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>通过对词汇、词法，以及句法的详细比较研究，学者们发现所有上述语言都源自一个被称为</t>
+          <t>的共同祖先，一门极有可能在公元前六千年某个时期被使用的语言。</t>
         </is>
       </c>
     </row>
@@ -854,14 +882,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>【章节大标题原文】</t>
+          <t>【译者：机翻】</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>印欧语或原始印欧语</t>
+          <t>学者们通过对词汇、词法，以及句法的详细比较研究，发现上述语言都源自一个称为印欧语或原始印欧语的共同祖先，而这门语言可能使用于公元前六千年的某个时期。</t>
         </is>
       </c>
     </row>
@@ -873,102 +901,102 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>【章节大标题原文】</t>
+          <t>【译者：机翻】</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>（地区？）</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>的共同祖先，一门极有可能在公元前六千年某个时期被使用的语言。</t>
+          <t>Over time,it is supposed,the people who spoke this original language gradually dispersed throughout Europe,Asia,and India,and the language changed differently in different places until the variety of languages belonging to this family gradually appeared.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>【章节大标题原文】</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+          <t>序言</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>学者们通过对词汇、词法，以及句法的详细比较研究，发现上述语言都源自一个称为印欧语或原始印欧语的共同祖先，而这门语言可能使用于公元前六千年的某个时期。</t>
+          <t>据推测，随时代变迁，这一原始语言的使用者逐渐分散开来，遍布于欧洲、亚洲，以及印度，这门语言也随地域变化而变化着，直至属于这一语系的多种语言渐渐形成。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>INTRODUCTION</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>序言</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>【译者：机翻】</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Over time,it is supposed,the people who spoke this original language gradually dispersed throughout Europe,Asia,and India,and the language changed differently in different places until the variety of languages belonging to this family gradually appeared.</t>
+          <t>据推测，该原始语言的使用者随时间变化逐渐分散迁徙到欧洲、亚洲，以及印度，而这门语言也随地域渐渐变化为同一语系的不同语言。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>INTRODUCTION</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>（地区？）</t>
-        </is>
-      </c>
+          <t>【二级标题原文】</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>据推测，随时代变迁，这一原始语言的使用者逐渐分散开来，遍布于欧洲、亚洲，以及印度，这门语言也随地域变化而变化着，直至属于这一语系的多种语言渐渐形成。</t>
+          <t>No direct evidence-that is,written or archaeological evidence-survives either for PIE or for the people who spoke it.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>【章节大标题译文】</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>【二级标题原文】</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>据推测，该原始语言的使用者随时间变化逐渐分散迁徙到欧洲、亚洲，以及印度，而这门语言也随地域渐渐变化为同一语系的不同语言。</t>
+          <t>然而没有现存的直接证据，即书面或考古学上的证据，能够证明</t>
         </is>
       </c>
     </row>
@@ -980,18 +1008,18 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>【章节大标题译文】</t>
+          <t>【二级标题原文】</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>【译者：机翻】</t>
+          <t>【译者：Lanx】</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>No direct evidence-that is,written or archaeological evidence-survives either for PIE or for the people who spoke it.</t>
+          <t>原始印欧语</t>
         </is>
       </c>
     </row>
@@ -1003,14 +1031,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>【译者：机翻】</t>
+          <t xml:space="preserve">The Latin Language </t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>然而没有现存的直接证据，即书面或考古学上的证据，能够证明</t>
+          <t>及其使用者的存在。</t>
         </is>
       </c>
     </row>
@@ -1022,18 +1050,18 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t xml:space="preserve">The Latin Language </t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>【译者：机翻】</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>（地区？）</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>原始印欧语</t>
+          <t>然而没有现存书面或考古上的证据，可以直接证明原始印欧语及其使用者的存在</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1073,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>【译者：机翻】</t>
+          <t xml:space="preserve">The Latin Language </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1056,7 +1084,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>及其使用者的存在。</t>
+          <t>What is known of the language comes from the comparative study of the languages that survive.</t>
         </is>
       </c>
     </row>
@@ -1068,14 +1096,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>序言</t>
+          <t>【二级标题译文】</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>然而没有现存书面或考古上的证据，可以直接证明原始印欧语及其使用者的存在</t>
+          <t>人们</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1115,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>序言</t>
+          <t>【二级标题译文】</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1098,7 +1126,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>What is known of the language comes from the comparative study of the languages that survive.</t>
+          <t>（只能）</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1138,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>序言</t>
+          <t>【二级标题译文】</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1121,74 +1149,38 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>人们</t>
+          <t>通过对现存语言的比较研究来了解它。</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>【正文原文】</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>【章节标题原文】</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>（只能）</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>【章节标题原文】</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>【译者：机翻】</t>
-        </is>
-      </c>
+          <t>【正文原文】</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>通过对现存语言的比较研究来了解它。</t>
+          <t>The study of these languages began at the end of the eighteenth century when Sir William Jones,a lawyer and student of eastern languages,first asserted publicly that Greek,Latin,and the language of ancient India,Sanskrit,were descended from a common source.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>【章节标题原文】</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>The study of these languages began at the end of the eighteenth century when Sir William Jones,a lawyer and student of eastern languages,first asserted publicly that Greek,Latin,and the language of ancient India,Sanskrit,were descended from a common source.</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1227,7 +1219,11 @@
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
@@ -1242,11 +1238,7 @@
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
@@ -1261,7 +1253,11 @@
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
@@ -1272,15 +1268,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>19世纪初，弗朗茨-博普（Franz Bopp）比较了拉丁语、希腊语、梵语、古波斯语及日耳曼语族（ the Germanic languages，英语正是其中一员 ）中的动词形式，开启了印欧语系的科学研究。</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19世纪初，弗朗茨-博普（Franz Bopp）比较了拉丁语、希腊语、梵语、古波斯语及日耳曼语族（ the Germanic languages，英语正是其中一员 ）中的动词形式，开启了印欧语系的科学研究。</t>
+          <t>The Indo-European languages have been analyzed and divided into various subgroups,or dialects,and Latin belongs to one called Italic because the languages of this subgroup were all spoken on the Italian peninsula.</t>
         </is>
       </c>
     </row>
@@ -1291,11 +1291,7 @@
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>The Indo-European languages have been analyzed and divided into various subgroups,or dialects,and Latin belongs to one called Italic because the languages of this subgroup were all spoken on the Italian peninsula.</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
@@ -1310,7 +1306,11 @@
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【词汇表】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1340,7 +1340,11 @@
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
@@ -1355,7 +1359,11 @@
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
@@ -1370,11 +1378,7 @@
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
@@ -1419,7 +1423,11 @@
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
@@ -1434,7 +1442,11 @@
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
@@ -1449,11 +1461,7 @@
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
@@ -1468,7 +1476,11 @@
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
@@ -1498,7 +1510,11 @@
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
@@ -1509,7 +1525,11 @@
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
@@ -1520,11 +1540,7 @@
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
@@ -1539,7 +1555,11 @@
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
@@ -1569,7 +1589,11 @@
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
@@ -1584,7 +1608,11 @@
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
@@ -1599,11 +1627,7 @@
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
@@ -1618,7 +1642,11 @@
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
@@ -1633,7 +1661,11 @@
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
@@ -1648,11 +1680,7 @@
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
@@ -1667,7 +1695,11 @@
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
@@ -1676,7 +1708,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
@@ -1693,7 +1729,11 @@
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
@@ -1708,7 +1748,11 @@
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
@@ -1723,11 +1767,7 @@
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
@@ -1736,7 +1776,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
@@ -1777,7 +1821,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
@@ -1794,7 +1842,11 @@
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
@@ -1811,7 +1863,7 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>【译者：Lanx】</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -1858,7 +1910,11 @@
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
@@ -1873,11 +1929,7 @@
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
@@ -1901,7 +1953,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
@@ -1940,7 +1996,11 @@
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
@@ -1957,7 +2017,7 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>【译者：Lanx】</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -1968,24 +2028,16 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>愈发尖锐</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -1993,52 +2045,48 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Despite setbacks both external and internal, Rome gradually expanded its influence, through treaty and conquest, until by the end of the third century B.c.E. it controlled most of modern-day Italy and had made inroads into the eastern Mediterranean as well.</t>
+          <t>愈发尖锐</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>尽管内外交困，罗马还是通过条约和征服逐渐扩大了势力。至公元前三世纪末，罗马控制着今意大利的大部分地区，并侵入了东地中海。</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>尽管内外交困，罗马依然通过谈判与征服逐渐扩大了影响力，到公元前三世纪末，已经控制了如今意大利的大部分地区，并且向东地中海扩张。</t>
+          <t>Despite setbacks both external and internal, Rome gradually expanded its influence, through treaty and conquest, until by the end of the third century B.c.E. it controlled most of modern-day Italy and had made inroads into the eastern Mediterranean as well.</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Latin literature first appears in the later part of this period of political expansion. </t>
+          <t>尽管内外交困，罗马还是通过条约和征服逐渐扩大了势力。至公元前三世纪末，罗马控制着今意大利的大部分地区，并侵入了东地中海。</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2101,7 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>就在这一政治扩张时期的后期，拉丁语文学首次出现。</t>
+          <t>尽管内外交困，罗马依然通过谈判与征服逐渐扩大了影响力，到公元前三世纪末，已经控制了如今意大利的大部分地区，并且向东地中海扩张。</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2116,7 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">The most prominent authors of this period whose works survive are the comic poets Plautus (254 -184 B.c.E.) and Terence (185?-159), the epic poet Ennius (239 169), and the orator, historian, and essayist Cato (234-149). </t>
+          <t xml:space="preserve">Latin literature first appears in the later part of this period of political expansion. </t>
         </is>
       </c>
     </row>
@@ -2081,13 +2129,13 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>【译者：Lanx】</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>该时期最著名的作家有——喜剧诗人普劳图斯（Plautus，公元前 254 - 184 年）和泰伦提乌斯（Terence，公元前 185 - 159 年）、史诗作者恩纽斯（Ennius，公元前 239 - 169 年）以及演说家、历史学家和散文作家加图（Cato，公元前 234 - 149 年）。（人名术语统一</t>
+          <t>就在这一政治扩张时期的后期，拉丁语文学首次出现。</t>
         </is>
       </c>
     </row>
@@ -2098,11 +2146,15 @@
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">The language of the comedians is often thought to contain evidence of the way Latin was actually spoken at this time because the characters of the comic plays are drawn from all walks of life. </t>
+          <t xml:space="preserve">The most prominent authors of this period whose works survive are the comic poets Plautus (254 -184 B.c.E.) and Terence (185?-159), the epic poet Ennius (239 169), and the orator, historian, and essayist Cato (234-149). </t>
         </is>
       </c>
     </row>
@@ -2117,14 +2169,14 @@
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>而喜剧中的角色三教九流，可以说演员们使用的即是实际生活中的口语。</t>
+          <t>该时期最著名的作家有——喜剧诗人普劳图斯（Plautus，公元前 254 - 184 年）和泰伦提乌斯（Terence，公元前 185 - 159 年）、史诗作者恩纽斯（Ennius，公元前 239 - 169 年）以及演说家、历史学家和散文作家加图（Cato，公元前 234 - 149 年）。（人名术语统一</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -2132,14 +2184,14 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>因为各个社会阶层的角色在喜剧中都有一席之地，彼时人们真正在讲的拉丁语被认为在台词中有所体现</t>
+          <t xml:space="preserve">The language of the comedians is often thought to contain evidence of the way Latin was actually spoken at this time because the characters of the comic plays are drawn from all walks of life. </t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -2147,7 +2199,7 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ennius, who spoke both Greek and Oscan in addition to Latin, borrowed and adapted many features of the Greek language and was one of the first writers of epic poetry in Latin.</t>
+          <t>而喜剧中的角色三教九流，可以说演员们使用的即是实际生活中的口语。</t>
         </is>
       </c>
     </row>
@@ -2160,46 +2212,54 @@
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>【译者：Lanx】</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>恩纽斯除了会说拉丁语外，还会说希腊语和奥斯坎语，他借用并改造了许多希腊语（ the Greek language）的特征，也是最早使用拉丁语创作史诗的作家之一</t>
+          <t>因为各个社会阶层的角色在喜剧中都有一席之地，彼时人们真正在讲的拉丁语被认为在台词中有所体现</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【词汇表】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>恩纽斯不光会说拉丁语，还会希腊语和奥斯坎语。他不仅借用并改造了许多希腊语（ the Greek language）的特征，也是最早使用拉丁语创作史诗的作家之一</t>
+          <t>Ennius, who spoke both Greek and Oscan in addition to Latin, borrowed and adapted many features of the Greek language and was one of the first writers of epic poetry in Latin.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve"> His style greatly influenced later poets, and he may be said to be the </t>
+          <t>恩纽斯除了会说拉丁语外，还会说希腊语和奥斯坎语，他借用并改造了许多希腊语（ the Greek language）的特征，也是最早使用拉丁语创作史诗的作家之一</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -2207,26 +2267,22 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>，他的风格极大地影响了后来的诗人，可以说他……（这里转页</t>
+          <t>恩纽斯不光会说拉丁语，还会希腊语和奥斯坎语。他不仅借用并改造了许多希腊语（ the Greek language）的特征，也是最早使用拉丁语创作史诗的作家之一</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>【译者注释】</t>
-        </is>
-      </c>
+      <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>【译者：Lanx】</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">注释：1. Faliscan was spoken in the area of Italy called Etruria (central Italy), Oscan in Campania (southern Italy), and Umbrian in Umbria (north-central Italy). </t>
+          <t xml:space="preserve"> His style greatly influenced later poets, and he may be said to be the </t>
         </is>
       </c>
     </row>
@@ -2237,22 +2293,30 @@
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>法利希语使用于伊特鲁里亚地区（位于意大利中部），奥斯坎语使用于坎帕尼亚（意大利南部），翁布里亚语使用于翁布里亚（意大利中北部）。</t>
+          <t>，他的风格极大地影响了后来的诗人，可以说他……（这里转页</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>The Samnites, an ancient Italian people with whom Rome came into conflict early, spoke Oscan</t>
+          <t xml:space="preserve">注释：1. Faliscan was spoken in the area of Italy called Etruria (central Italy), Oscan in Campania (southern Italy), and Umbrian in Umbria (north-central Italy). </t>
         </is>
       </c>
     </row>
@@ -2267,29 +2331,33 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>萨姆尼特人是支使用奥斯坎语的古意大利民族，早年间与罗马人有过冲突。</t>
+          <t>法利希语使用于伊特鲁里亚地区（位于意大利中部），奥斯坎语使用于坎帕尼亚（意大利南部），翁布里亚语使用于翁布里亚（意大利中北部）。</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>萨姆尼特人，一支说奥斯坎语的古意大利民族，早年间与罗马人发生过冲突</t>
+          <t>The Samnites, an ancient Italian people with whom Rome came into conflict early, spoke Oscan</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -2297,48 +2365,52 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>序号35，页数3（拆分：？，？）（机翻：？，？）（人翻：？，？）（第一次润色（按句）：？，？）（第一次校对：？，？）（第二次润色（按意群）：？，？）（第二次校对：？，？）（终润（按段落）：？，？）（终校：？，？）（附加评论/修改建议：？，？）（排版/美化：？，？）（美化后期再做）</t>
+          <t>萨姆尼特人是支使用奥斯坎语的古意大利民族，早年间与罗马人有过冲突。</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr"/>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">first to have established a literary language-a written language with increasingly strict rules of vocabulary and syntax. </t>
+          <t>萨姆尼特人，一支说奥斯坎语的古意大利民族，早年间与罗马人发生过冲突</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【分工】</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>他的风格极大地影响了后来的诗人，可以说他是第一位确立了文学语言（ literary language）</t>
+          <t>序号35，页数3（拆分：？，？）（机翻：？，？）（人翻：？，？）（第一次润色（按句）：？，？）（第一次校对：？，？）（第二次润色（按意群）：？，？）（第二次校对：？，？）（终润（按段落）：？，？）（终校：？，？）（附加评论/修改建议：？，？）（排版/美化：？，？）（美化后期再做）</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>（规范）</t>
+          <t xml:space="preserve">first to have established a literary language-a written language with increasingly strict rules of vocabulary and syntax. </t>
         </is>
       </c>
     </row>
@@ -2353,26 +2425,26 @@
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>的人（一种词汇和句法都逐渐严谨的的书面语）。</t>
+          <t>他的风格极大地影响了后来的诗人，可以说他是第一位确立了文学语言（ literary language）</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>【译者：Lanx】</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Together, these authors represent what may be called early Latin.</t>
+          <t>（规范）</t>
         </is>
       </c>
     </row>
@@ -2383,18 +2455,22 @@
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>这些作家共同代表了早期拉丁语。</t>
+          <t>的人（一种词汇和句法都逐渐严谨的的书面语）。</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【词汇表】</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -2402,7 +2478,7 @@
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>这些作家共同写就了所谓的早期拉丁语。</t>
+          <t>Together, these authors represent what may be called early Latin.</t>
         </is>
       </c>
     </row>
@@ -2417,41 +2493,45 @@
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>这些作家作品共同贡献了所谓的早期拉丁语（ early Latin）</t>
+          <t>这些作家共同代表了早期拉丁语。</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>宗之：这些作家都是早期拉丁语的代表</t>
+          <t>这些作家共同写就了所谓的早期拉丁语。</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>【译者：Lanx】</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Over the next two centuries to the end of the first centuryB.C.E., Roman authors, much influenced by the Greek literature with which they had come into contact after the conquest of Greece, continued to develop a literary language in Iatin.</t>
+          <t>这些作家作品共同贡献了所谓的早期拉丁语（ early Latin）</t>
         </is>
       </c>
     </row>
@@ -2462,18 +2542,22 @@
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>在接下来的两个世纪到公元前一世纪末，罗马征服了希腊，罗马作家得以接触希腊文学并深受其影响，继续用拉丁语发展文学语言。</t>
+          <t>宗之：这些作家都是早期拉丁语的代表</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -2481,7 +2565,7 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>在接下来的两个世纪里，在罗马征服希腊后，作家们得以接触希腊文学并深受其影响，继续发展着属于拉丁语的文学语言，直到公元前一世纪末。</t>
+          <t>Over the next two centuries to the end of the first centuryB.C.E., Roman authors, much influenced by the Greek literature with which they had come into contact after the conquest of Greece, continued to develop a literary language in Iatin.</t>
         </is>
       </c>
     </row>
@@ -2496,70 +2580,78 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>直到公元前一世纪末的两个世纪里，罗马作家于希腊征服后，得以接触到古希腊文学（the Greek literature），深受其影响的同时，也为拉丁语文学语言的发展添砖加瓦</t>
+          <t>在接下来的两个世纪到公元前一世纪末，罗马征服了希腊，罗马作家得以接触希腊文学并深受其影响，继续用拉丁语发展文学语言。</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">They established rules of spelling, morphology, syntax, and vocabulary, and also </t>
+          <t>在接下来的两个世纪里，在罗马征服希腊后，作家们得以接触希腊文学并深受其影响，继续发展着属于拉丁语的文学语言，直到公元前一世纪末。</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">distinguished </t>
+          <t>直到公元前一世纪末的两个世纪里，罗马作家于希腊征服后，得以接触到古希腊文学（the Greek literature），深受其影响的同时，也为拉丁语文学语言的发展添砖加瓦</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>between correct usages for poetry and for prose.</t>
+          <t xml:space="preserve">They established rules of spelling, morphology, syntax, and vocabulary, and also </t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>他们制定了拼写、词法、句法和词的规则，还区分了诗歌和散文的正确用法。</t>
+          <t xml:space="preserve">distinguished </t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>他们确立了这一文学语言的拼读体系、词法、句法和语汇，还对诗歌与散文（各自的范畴）作了合理区分。</t>
+          <t>between correct usages for poetry and for prose.</t>
         </is>
       </c>
     </row>
@@ -2570,11 +2662,15 @@
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>他们制定了拼写、词法、句法和词汇的规范，</t>
+          <t>他们制定了拼写、词法、句法和词的规则，还区分了诗歌和散文的正确用法。</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2685,7 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>还区分了这些规则</t>
+          <t>他们确立了这一文学语言的拼读体系、词法、句法和语汇，还对诗歌与散文（各自的范畴）作了合理区分。</t>
         </is>
       </c>
     </row>
@@ -2604,141 +2700,181 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>在诗歌和散文中的正确用法。结果是，在共和国晚期与帝国早期（约公元前100至公元100年），有文化的罗马民众均参照该规范来使用这种拉丁语，我们常称之为古典拉丁语 （classical Iatin）</t>
+          <t>他们制定了拼写、词法、句法和词汇的规范，</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>The result is usually called classical Iatin, the language that was written and spoken</t>
+          <t>还区分了这些规则</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr"/>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>在诗歌和散文中的正确用法。结果是，在共和国晚期与帝国早期（约公元前100至公元100年），有文化的罗马民众均参照该规范来使用这种拉丁语，我们常称之为古典拉丁语 （classical Iatin）</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>by the educated Roman populace during the period of the late Republic and early Empire (roughly 100B.C.E.-100C.E.).</t>
+          <t>The result is usually called classical Iatin, the language that was written and spoken</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>最后的成果通常被称为古典拉丁语，即共和国晚期和帝国早期（约公元前 100 年至公元100 年）3为受过教育的罗马民众所书写和叙说（？）的语言2。</t>
+          <t>by the educated Roman populace during the period of the late Republic and early Empire (roughly 100B.C.E.-100C.E.).</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>最后的成果通常被称为古典拉丁语，一门在共和国晚期与帝国早期（约公元前100至公元100年），受过教育的罗马民众所写所说的语言</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Among the authors who wrote classical Latin are, in prose</t>
+          <t>最后的成果通常被称为古典拉丁语，即共和国晚期和帝国早期（约公元前 100 年至公元100 年）3为受过教育的罗马民众所书写和叙说（？）的语言2。</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>:</t>
+          <t>最后的成果通常被称为古典拉丁语，一门在共和国晚期与帝国早期（约公元前100至公元100年），受过教育的罗马民众所写所说的语言</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Caesar(100-44 B.</t>
+          <t>Among the authors who wrote classical Latin are, in prose</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>:</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>.E.), Cicero(106-43 B.</t>
+          <t>Caesar(100-44 B.</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
@@ -2751,16 +2887,24 @@
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>.E.), and Iivy (59B.</t>
+          <t>.E.), Cicero(106-43 B.</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
@@ -2777,14 +2921,22 @@
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>.E.-17</t>
+          <t>.E.), and Iivy (59B.</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
@@ -2799,40 +2951,52 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>.E.); and in poetry: Catullus (84?-54?</t>
+          <t>.E.-17</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr"/>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr"/>
-      <c r="C151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>.E.); and in poetry: Catullus (84?-54?</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr"/>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2843,18 +3007,22 @@
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>.E.), Vergil(70-19</t>
+          <t>.</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2865,18 +3033,26 @@
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>.</t>
+          <t>.E.), Vergil(70-19</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr"/>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2887,14 +3063,14 @@
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>.E.), and Horace (65-8B.C.E.).</t>
+          <t>.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -2902,69 +3078,53 @@
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>以散文形式写作古典拉丁文的作家有：恺撒（公元前 100-44 年）、西塞罗（公元前 106-43 年）和李维（公元前 59 年-公元前 17 年）；写作诗歌的有：卡图卢斯（公元前 84 ？年至公元前 54 ？年）、维吉尔（公元前 70 年至公元前 19 年）和贺拉斯（公元前 65 年至公元前 8 年）。</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr"/>
-      <c r="C159" t="inlineStr"/>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>古典拉丁语作家中写散文的有：恺撒（公元前 100-44 年）、西塞罗（公元前 106-43 年）和李维（公元前 59 年-公元前 17 年）；写诗歌的有：卡图卢斯（公元前 84 ？年至公元前 54 ？年）、维吉尔（公元前 70 年至公元前 19 年）和贺拉斯（公元前 65 年至公元前 8 年）。</t>
+          <t>.E.), and Horace (65-8B.C.E.).</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>This book introduces the student to the language written by these authors and others of the same period.</t>
+          <t>以散文形式写作古典拉丁文的作家有：恺撒（公元前 100-44 年）、西塞罗（公元前 106-43 年）和李维（公元前 59 年-公元前 17 年）；写作诗歌的有：卡图卢斯（公元前 84 ？年至公元前 54 ？年）、维吉尔（公元前 70 年至公元前 19 年）和贺拉斯（公元前 65 年至公元前 8 年）。</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>本书向学生介绍了为这些作家以及同一时期其他作家所书写的语言。</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr"/>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>The Indo-European languages have been analyzed and divided into various subgroups,or dialects,and Latin belongs to one called Italic because the languages of this subgroup were all spoken on the Italian peninsula.</t>
-        </is>
-      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>本书将使学生对上述作家及同一时期其余作家所使用的语言有所了解</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2977,14 +3137,14 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>本书将介绍的拉丁语，是上述作家以及同时期其他作家所使用的拉丁语，并将指出其在散文与诗歌中的用法区别。</t>
+          <t>古典拉丁语作家中写散文的有：恺撒（公元前 100-44 年）、西塞罗（公元前 106-43 年）和李维（公元前 59 年-公元前 17 年）；写诗歌的有：卡图卢斯（公元前 84 ？年至公元前 54 ？年）、维吉尔（公元前 70 年至公元前 19 年）和贺拉斯（公元前 65 年至公元前 8 年）。</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -2992,7 +3152,7 @@
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>但就大部分所介绍的古典拉丁语规则而言</t>
+          <t>This book introduces the student to the language written by these authors and others of the same period.</t>
         </is>
       </c>
     </row>
@@ -3005,46 +3165,62 @@
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>The Indo-European languages have been analyzed and divided into various subgroups,or dialects,and Latin belongs to one called Italic because the languages of this subgroup were all spoken on the Italian peninsula.</t>
+          <t>19世纪初，弗朗茨-博普（Franz Bopp）比较了拉丁语、希腊语、梵语、古波斯语及日耳曼语族（ the Germanic languages，英语正是其中一员 ）中的动词形式，开启了印欧语系的科学研究。</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">，我们可假定适用于该时期的所有文学作品。  </t>
+          <t>本书向学生介绍了为这些作家以及同一时期其他作家所书写的语言。</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr"/>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Distinctions of usage between prose and poetry wil be pointed out, </t>
+          <t>本书将使学生对上述作家及同一时期其余作家所使用的语言有所了解</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>but for the most part</t>
+          <t>本书将介绍的拉丁语，是上述作家以及同时期其他作家所使用的拉丁语，并将指出其在散文与诗歌中的用法区别。</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr"/>
-      <c r="C168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>19世纪初，弗朗茨-博普（Franz Bopp）比较了拉丁语、希腊语、梵语、古波斯语及日耳曼语族（ the Germanic languages，英语正是其中一员 ）中的动词形式，开启了印欧语系的科学研究。</t>
+        </is>
+      </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>, the rules of classical Latin presented here may be presumed to hold true for the literature</t>
+          <t>但就大部分所介绍的古典拉丁语规则而言</t>
         </is>
       </c>
     </row>
@@ -3053,11 +3229,7 @@
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> of this period as a whole.</t>
-        </is>
-      </c>
+      <c r="E169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3066,22 +3238,18 @@
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>The Indo-European languages have been analyzed and divided into various subgroups,or dialects,and Latin belongs to one called Italic because the languages of this subgroup were all spoken on the Italian peninsula.</t>
-        </is>
-      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t xml:space="preserve">本书将指出散文和诗歌在用法上的区别，但在大多数情况下，本书介绍的古典拉丁语规则可以认为适用于这一时期的所有文学作品。 </t>
+          <t xml:space="preserve">，我们可假定适用于该时期的所有文学作品。  </t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -3089,78 +3257,66 @@
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>8.2 改到这里</t>
+          <t xml:space="preserve">Distinctions of usage between prose and poetry wil be pointed out, </t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>【批注】</t>
-        </is>
-      </c>
+      <c r="A172" t="inlineStr"/>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>8.3 同上</t>
+          <t>but for the most part</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
-        </is>
-      </c>
+      <c r="A173" t="inlineStr"/>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Pronunciation of Classical Latin</t>
+          <t>, the rules of classical Latin presented here may be presumed to hold true for the literature</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A174" t="inlineStr"/>
       <c r="B174" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>19世纪初，弗朗茨-博普（Franz Bopp）比较了拉丁语、希腊语、梵语、古波斯语及日耳曼语族（ the Germanic languages，英语正是其中一员 ）中的动词形式，开启了印欧语系的科学研究。</t>
+        </is>
+      </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>古典拉丁语的发音</t>
+          <t xml:space="preserve"> of this period as a whole.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>The Indo-European languages have been analyzed and divided into various subgroups,or dialects,and Latin belongs to one called Italic because the languages of this subgroup were all spoken on the Italian peninsula.</t>
-        </is>
-      </c>
+      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Although there must have been variations in the pronunciation of classical Iatin such as are evident in any modern language, there is considerable ancient evidence for a standard in pronunciation, and rules approximating that standard are presented here."</t>
+          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -3168,7 +3324,7 @@
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8.2 改到这里</t>
         </is>
       </c>
     </row>
@@ -3183,48 +3339,48 @@
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">古典拉丁语和任何现代语言一样必然存在着发音的变化，不过相当多的古代证据证明它的发音是有标准的，这里介绍的就是接近这一标准的规则 </t>
+          <t>8.3 同上</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>The Indo-European languages have been analyzed and divided into various subgroups,or dialects,and Latin belongs to one called Italic because the languages of this subgroup were all spoken on the Italian peninsula.</t>
-        </is>
-      </c>
+      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>尽管古典拉丁语同任何现代语言一样不可避免地有着发音的流变，但相当多的古代证据表明它曾有一套标准的发音，本书接下来便要介绍一套近似的发音规则。</t>
+          <t>Pronunciation of Classical Latin</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
-      <c r="C179" t="inlineStr"/>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>19世纪初，弗朗茨-博普（Franz Bopp）比较了拉丁语、希腊语、梵语、古波斯语及日耳曼语族（ the Germanic languages，英语正是其中一员 ）中的动词形式，开启了印欧语系的科学研究。</t>
+        </is>
+      </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>The rules for pronouncing classical Iatin have been reconstructed from several types of evidence：</t>
+          <t>古典拉丁语的发音</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -3232,41 +3388,41 @@
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>古典拉丁语发音规则根据以下几种证据重新构拟</t>
+          <t>Although there must have been variations in the pronunciation of classical Iatin such as are evident in any modern language, there is considerable ancient evidence for a standard in pronunciation, and rules approximating that standard are presented here."</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">本书将指出散文和诗歌在用法上的区别，但在大多数情况下，本书介绍的古典拉丁语规则可以认为适用于这一时期的所有文学作品。 </t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>The Indo-European languages have been analyzed and divided into various subgroups,or dialects,and Latin belongs to one called Italic because the languages of this subgroup were all spoken on the Italian peninsula.</t>
-        </is>
-      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>古典拉丁语的发音规则由以下几种证据重新构拟而成：</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
-      <c r="C182" t="inlineStr"/>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>19世纪初，弗朗茨-博普（Franz Bopp）比较了拉丁语、希腊语、梵语、古波斯语及日耳曼语族（ the Germanic languages，英语正是其中一员 ）中的动词形式，开启了印欧语系的科学研究。</t>
+        </is>
+      </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. the statements of Latin grammarians and Latin authors on specific points of Latin pronunciation. </t>
+          <t xml:space="preserve">古典拉丁语和任何现代语言一样必然存在着发音的变化，不过相当多的古代证据证明它的发音是有标准的，这里介绍的就是接近这一标准的规则 </t>
         </is>
       </c>
     </row>
@@ -3281,41 +3437,41 @@
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>1. 如通过拉丁语语法学家和拉丁语作者对拉丁语发音的具体论述。</t>
+          <t>尽管古典拉丁语同任何现代语言一样不可避免地有着发音的流变，但相当多的古代证据表明它曾有一套标准的发音，本书接下来便要介绍一套近似的发音规则。</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>The Indo-European languages have been analyzed and divided into various subgroups,or dialects,and Latin belongs to one called Italic because the languages of this subgroup were all spoken on the Italian peninsula.</t>
-        </is>
-      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>1.拉丁语法学家和拉丁语作者对其发音要点的论述</t>
+          <t>The rules for pronouncing classical Iatin have been reconstructed from several types of evidence：</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>19世纪初，弗朗茨-博普（Franz Bopp）比较了拉丁语、希腊语、梵语、古波斯语及日耳曼语族（ the Germanic languages，英语正是其中一员 ）中的动词形式，开启了印欧语系的科学研究。</t>
+        </is>
+      </c>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve"> The Latin grammarians were active much later than the period assigned to classical Latin, but they cite the work of earlier Latin authors and confirm features of pronunciation known from other sources.</t>
+          <t>古典拉丁语发音规则根据以下几种证据重新构拟</t>
         </is>
       </c>
     </row>
@@ -3330,48 +3486,48 @@
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>拉丁语语法学家的活跃时间远远晚于古典拉丁语的时期，但他们引用了早期拉丁语作者的作品，并从其他来源确定了发音特点。</t>
+          <t>古典拉丁语的发音规则由以下几种证据重新构拟而成：</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">本书将指出散文和诗歌在用法上的区别，但在大多数情况下，本书介绍的古典拉丁语规则可以认为适用于这一时期的所有文学作品。 </t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>The Indo-European languages have been analyzed and divided into various subgroups,or dialects,and Latin belongs to one called Italic because the languages of this subgroup were all spoken on the Italian peninsula.</t>
-        </is>
-      </c>
+      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>虽然语法学家们活跃的时间远远晚于古典拉丁语时期，但他们援引先人的作品，并根据其他原始资料确定了发音特点</t>
+          <t xml:space="preserve">1. the statements of Latin grammarians and Latin authors on specific points of Latin pronunciation. </t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
-      <c r="C188" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>19世纪初，弗朗茨-博普（Franz Bopp）比较了拉丁语、希腊语、梵语、古波斯语及日耳曼语族（ the Germanic languages，英语正是其中一员 ）中的动词形式，开启了印欧语系的科学研究。</t>
+        </is>
+      </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. the orthography, or spelling, of Latin words in inscriptions. </t>
+          <t>1. 如通过拉丁语语法学家和拉丁语作者对拉丁语发音的具体论述。</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>【译者注释】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -3379,41 +3535,41 @@
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2. 如通过铭文中拉丁语词汇（译者注：此后简写为“拉丁词”）的正字法或拼写。</t>
+          <t>1.拉丁语法学家和拉丁语作者对其发音要点的论述</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">本书将指出散文和诗歌在用法上的区别，但在大多数情况下，本书介绍的古典拉丁语规则可以认为适用于这一时期的所有文学作品。 </t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>The Indo-European languages have been analyzed and divided into various subgroups,or dialects,and Latin belongs to one called Italic because the languages of this subgroup were all spoken on the Italian peninsula.</t>
-        </is>
-      </c>
+      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2.铭文中拉丁单词的正字法或拼法</t>
+          <t xml:space="preserve"> The Latin grammarians were active much later than the period assigned to classical Latin, but they cite the work of earlier Latin authors and confirm features of pronunciation known from other sources.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
-      <c r="C191" t="inlineStr"/>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>19世纪初，弗朗茨-博普（Franz Bopp）比较了拉丁语、希腊语、梵语、古波斯语及日耳曼语族（ the Germanic languages，英语正是其中一员 ）中的动词形式，开启了印欧语系的科学研究。</t>
+        </is>
+      </c>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Ancient spelling, both in Latin and in other ancient languages, was considerably less standardized than modern spelling. Variations in spelling usually indicate differences in pronunciation.</t>
+          <t>拉丁语语法学家的活跃时间远远晚于古典拉丁语的时期，但他们引用了早期拉丁语作者的作品，并从其他来源确定了发音特点。</t>
         </is>
       </c>
     </row>
@@ -3428,26 +3584,22 @@
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>无论是拉丁语还是其他古代语言，古代拼写都远没有现代拼写那么标准化。拼写不同通常也标示着发音不同。</t>
+          <t>虽然语法学家们活跃的时间远远晚于古典拉丁语时期，但他们援引先人的作品，并根据其他原始资料确定了发音特点</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">本书将指出散文和诗歌在用法上的区别，但在大多数情况下，本书介绍的古典拉丁语规则可以认为适用于这一时期的所有文学作品。 </t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>无论是拉丁语还是其他古典语言的古代拼写都远没有现代拼写那么标准化，</t>
+          <t xml:space="preserve">2. the orthography, or spelling, of Latin words in inscriptions. </t>
         </is>
       </c>
     </row>
@@ -3458,33 +3610,45 @@
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
-      <c r="C194" t="inlineStr"/>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>19世纪初，弗朗茨-博普（Franz Bopp）比较了拉丁语、希腊语、梵语、古波斯语及日耳曼语族（ the Germanic languages，英语正是其中一员 ）中的动词形式，开启了印欧语系的科学研究。</t>
+        </is>
+      </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>它们的拼写常随发音改变而改变</t>
+          <t>2. 如通过铭文中拉丁语词汇（译者注：此后简写为“拉丁词”）的正字法或拼写。</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr"/>
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>。</t>
+          <t>2.铭文中拉丁单词的正字法或拼法</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>3. the representation or transliteration of Latin words in other languages and the representation or transliteration of foreign words in Latin.</t>
+          <t>Ancient spelling, both in Latin and in other ancient languages, was considerably less standardized than modern spelling. Variations in spelling usually indicate differences in pronunciation.</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3667,7 @@
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>3.如通过拉丁词在其他语言中的呈现方式或音译，以及外来词在拉丁语中的表现或音译。</t>
+          <t>无论是拉丁语还是其他古代语言，古代拼写都远没有现代拼写那么标准化。拼写不同通常也标示着发音不同。</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3682,7 @@
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>3.拉丁词的其他语言</t>
+          <t>无论是拉丁语还是其他古典语言的古代拼写都远没有现代拼写那么标准化，</t>
         </is>
       </c>
     </row>
@@ -3529,39 +3693,27 @@
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>转录（译者注：指音位转录，一种目的为将原语言每一个音位的发音都尽可能准确地转录到目标语言的转录手段）</t>
+          <t>它们的拼写常随发音改变而改变</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A200" t="inlineStr"/>
       <c r="B200" t="inlineStr"/>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>，以及外来词的拉丁语转录。</t>
+          <t>。</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>【正文原文】</t>
-        </is>
-      </c>
+      <c r="A201" t="inlineStr"/>
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr">
         <is>
@@ -3571,7 +3723,7 @@
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>The transliteration of names, in particular, provides valuable information about how names were pronounced at different periods of Roman history.</t>
+          <t>3. the representation or transliteration of Latin words in other languages and the representation or transliteration of foreign words in Latin.</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3738,7 @@
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>尤其是人名的音译，提供了罗马历史上不同时期人名如何发音的宝贵信息。</t>
+          <t>3.如通过拉丁词在其他语言中的呈现方式或音译，以及外来词在拉丁语中的表现或音译。</t>
         </is>
       </c>
     </row>
@@ -3605,14 +3757,14 @@
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>尤其是人名的转录，向我们提供了罗马不同历史时期上人名是怎样发音的这一宝贵信息。</t>
+          <t>3.拉丁词的其他语言</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>【译者注释】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -3620,14 +3772,14 @@
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>注释：2. Some surviving texts, such as the orations of Cicero, suggest that classical Latin was both written and spoken.</t>
+          <t>转录（译者注：指音位转录，一种目的为将原语言每一个音位的发音都尽可能准确地转录到目标语言的转录手段）</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>【译者注释】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -3639,14 +3791,14 @@
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>注释：2. 一些留存的文本，如西塞罗的演讲，表明了既有书面古典拉丁语也有口头的。</t>
+          <t>，以及外来词的拉丁语转录。</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>【译者注释】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -3654,29 +3806,33 @@
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>注释：2. 一些留存的文本，如西塞罗的演讲，表明了古典拉丁语既有书面的也有口头的。</t>
+          <t>The transliteration of names, in particular, provides valuable information about how names were pronounced at different periods of Roman history.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
-      <c r="C207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>8.3 同上</t>
+          <t>尤其是人名的音译，提供了罗马历史上不同时期人名如何发音的宝贵信息。</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -3684,7 +3840,7 @@
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. There are, of course, variations in usage and style from author to author and from the beginning of this period to the end. </t>
+          <t>尤其是人名的转录，向我们提供了罗马不同历史时期上人名是怎样发音的这一宝贵信息。</t>
         </is>
       </c>
     </row>
@@ -3703,14 +3859,14 @@
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
-          <t>3.自然，这一阶段不同作者、不同时期的词汇用法和风格都有所不同。</t>
+          <t>注释：2. Some surviving texts, such as the orations of Cicero, suggest that classical Latin was both written and spoken.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -3718,7 +3874,7 @@
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
-          <t>It remains common to speak of Golden Age Latin (the Latin of first-century B.C.E. writers such as Caesar, Cicero, Vergil, and Horace) and Silver Age Latin (the Latin of first-century cE. writers such as Seneca andQuintilian).</t>
+          <t>注释：2. 一些留存的文本，如西塞罗的演讲，表明了古典拉丁语既有书面的也有口头的。</t>
         </is>
       </c>
     </row>
@@ -3729,22 +3885,18 @@
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
-          <t>黄金时代的拉丁语(公元前一世纪的作家如凯撒、西塞罗、维吉尔和贺拉斯使用的)和白银时代的拉丁语(公元一世纪塞内加和昆体良等作家使用的)仍然很常见。</t>
+          <t>8.2 改到这里</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -3752,22 +3904,26 @@
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>8.2 改到这里</t>
+          <t>3.自然，这一阶段不同作者、不同时期的词汇用法和风格都有所不同。</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
-      <c r="C213" t="inlineStr"/>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
-          <t>8.3 同上</t>
+          <t>It remains common to speak of Golden Age Latin (the Latin of first-century B.C.E. writers such as Caesar, Cicero, Vergil, and Horace) and Silver Age Latin (the Latin of first-century cE. writers such as Seneca andQuintilian).</t>
         </is>
       </c>
     </row>
@@ -3782,14 +3938,14 @@
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
-          <t>古典拉丁语二分为黄金时代的拉丁语(公元前一世纪的作家如凯撒、西塞罗、维吉尔和贺拉斯使用)"和"白银时代的拉丁语(公元一世纪塞内加和昆体良等作家使用)"这一说法仍然常见</t>
+          <t>黄金时代的拉丁语(公元前一世纪的作家如凯撒、西塞罗、维吉尔和贺拉斯使用的)和白银时代的拉丁语(公元一世纪塞内加和昆体良等作家使用的)仍然很常见。</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -3801,24 +3957,16 @@
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
-          <t>4. For this presentation of pronunciation the authors are indebted 1o W. S. Allen's Vox Latina (Cambridge, 1965).</t>
+          <t>古典拉丁语二分为黄金时代的拉丁语(公元前一世纪的作家如凯撒、西塞罗、维吉尔和贺拉斯使用)"和"白银时代的拉丁语(公元一世纪塞内加和昆体良等作家使用)"这一说法仍然常见</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A216" t="inlineStr"/>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4. 作者很感谢W. S. Allen的《Vox Latina》(剑桥，1965) </t>
-        </is>
-      </c>
+      <c r="E216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -3827,22 +3975,18 @@
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. 感谢W. S. Allen的《Vox Latina》(剑桥，1965) </t>
+          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -3850,26 +3994,22 @@
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
-          <t>序号36，页数4（拆分：？，？）（机翻：？，？）（人翻：？，？）（第一次润色（按句）：？，？）（第一次校对：？，？）（第二次润色（按意群）：？，？）（第二次校对：？，？）（终润（按段落）：？，？）（终校：？，？）（附加评论/修改建议：？，？）（排版/美化：？，？）（美化后期再做）</t>
+          <t>8.2 改到这里</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
+          <t>注释：2. 一些留存的文本，如西塞罗的演讲，表明了既有书面古典拉丁语也有口头的。</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
-          <t>4. the internal grammatical and poetic structure of Latin. This includes the evidence available from the metrical structure of Latin poetry.</t>
+          <t>4. For this presentation of pronunciation the authors are indebted 1o W. S. Allen's Vox Latina (Cambridge, 1965).</t>
         </is>
       </c>
     </row>
@@ -3880,11 +4020,15 @@
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
-      <c r="C220" t="inlineStr"/>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
-          <t>4. 如通过拉丁语的内部语法和诗歌结构，包括诗歌中的格律结构。</t>
+          <t xml:space="preserve">4. 作者很感谢W. S. Allen的《Vox Latina》(剑桥，1965) </t>
         </is>
       </c>
     </row>
@@ -3895,49 +4039,45 @@
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
-          <t>4.拉丁语的内在语法和诗歌结构，包括从拉丁诗歌格律结构所获的印证</t>
+          <t xml:space="preserve">4. 感谢W. S. Allen的《Vox Latina》(剑桥，1965) </t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【分工】</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
-      <c r="C222" t="inlineStr"/>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
-          <t>（？）这一句和下一句不知道要不要在前面加 “介绍了”，像是全段概括一样</t>
+          <t>序号36，页数4（拆分：？，？）（机翻：？，？）（人翻：？，？）（第一次润色（按句）：？，？）（第一次校对：？，？）（第二次润色（按意群）：？，？）（第二次校对：？，？）（终润（按段落）：？，？）（终校：？，？）（附加评论/修改建议：？，？）（排版/美化：？，？）（美化后期再做）</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
+          <t>注释：2. 一些留存的文本，如西塞罗的演讲，表明了既有书面古典拉丁语也有口头的。</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
-          <t>5. the etymology of Latin words and the development of Latin words in the Romance languages descended from Latin.</t>
+          <t>4. the internal grammatical and poetic structure of Latin. This includes the evidence available from the metrical structure of Latin poetry.</t>
         </is>
       </c>
     </row>
@@ -3948,11 +4088,15 @@
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
-      <c r="C224" t="inlineStr"/>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
-          <t>5. 如通过拉丁词的词源学及其在罗曼语族中的发展，而罗曼语族发源于拉丁语。</t>
+          <t>4. 如通过拉丁语的内部语法和诗歌结构，包括诗歌中的格律结构。</t>
         </is>
       </c>
     </row>
@@ -3967,33 +4111,41 @@
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>5.拉丁语的词源学，以及拉丁词汇在罗曼语族中的演变、发展</t>
+          <t>4.拉丁语的内在语法和诗歌结构，包括从拉丁诗歌格律结构所获的印证</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
-      <c r="C226" t="inlineStr"/>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>8.3 同上</t>
+          <t>（？）这一句和下一句不知道要不要在前面加 “介绍了”，像是全段概括一样</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr"/>
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>注释：2. 一些留存的文本，如西塞罗的演讲，表明了既有书面古典拉丁语也有口头的。</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Alphabet</t>
+          <t>5. the etymology of Latin words and the development of Latin words in the Romance languages descended from Latin.</t>
         </is>
       </c>
     </row>
@@ -4004,43 +4156,31 @@
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
-      <c r="C228" t="inlineStr"/>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>字母</t>
+          <t>5. 如通过拉丁词的词源学及其在罗曼语族中的发展，而罗曼语族发源于拉丁语。</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>【正文原文】</t>
-        </is>
-      </c>
+      <c r="A229" t="inlineStr"/>
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> The Latin alphabet is almost the same as the English alphabet. It lacks a j and a w.</t>
-        </is>
-      </c>
+      <c r="E229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A230" t="inlineStr"/>
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>拉丁字母与英语字母几乎相同，没有j和w。</t>
-        </is>
-      </c>
+      <c r="E230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4053,14 +4193,14 @@
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>拉丁字母与英语字母几乎相同，只少了j和w。</t>
+          <t>5.拉丁语的词源学，以及拉丁词汇在罗曼语族中的演变、发展</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
@@ -4068,18 +4208,22 @@
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>【原文脚注】</t>
+          <t>Alphabet</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr"/>
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
-          <t>OBSERVATIONS</t>
+          <t>8.2 改到这里</t>
         </is>
       </c>
     </row>
@@ -4090,15 +4234,11 @@
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
-          <t>注意</t>
+          <t>字母</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4249,7 @@
       <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
-          <t>1. k is used in only a few words, mostly of foreign origin. y and z occur in transcriptions of names and other words borrowed from Greek.</t>
+          <t xml:space="preserve"> The Latin alphabet is almost the same as the English alphabet. It lacks a j and a w.</t>
         </is>
       </c>
     </row>
@@ -4120,11 +4260,15 @@
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
-      <c r="C236" t="inlineStr"/>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
-          <t>1. k只出现在少数几个单词中，大多是外来语。y和z出现在名字转写以及其他希腊语借词中。</t>
+          <t>拉丁字母与英语字母几乎相同，没有j和w。</t>
         </is>
       </c>
     </row>
@@ -4135,45 +4279,45 @@
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
-          <t>k只在少数单词中出现，其中大多是外来词汇。y和z出现在名字转写以及其他希腊语借词中。</t>
+          <t>拉丁字母与英语字母几乎相同，只少了j和w。</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr"/>
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2. i can be either a consonant or a vowel. In some Latin texts, j is used as the sign of consonantal i. but in this book i is used for both the consonant and the vowel.</t>
+          <t>【原书脚注】</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="inlineStr">
         <is>
-          <t>【译者：Lanx】</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2． i既可以是辅音，也可以是元音。在一些拉丁文本中，j用来表示辅音i，但本书中，i既用于辅音又用于元音。</t>
+          <t>OBSERVATIONS</t>
         </is>
       </c>
     </row>
@@ -4188,18 +4332,22 @@
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2.i既可以是辅音也可以是元音。在一些拉丁文中用j来表示辅音i，但在本书中i用于辅音也用于元音。</t>
+          <t>注意</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="inlineStr"/>
-      <c r="C241" t="inlineStr"/>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. u also can be either a consonant or a vowel. In the classical period (and for several centuries afterward), Romans used the letter v to represent both the consonant and the vowel, and u was simply a rounded version of this letter. </t>
+          <t>1. k is used in only a few words, mostly of foreign origin. y and z occur in transcriptions of names and other words borrowed from Greek.</t>
         </is>
       </c>
     </row>
@@ -4210,15 +4358,11 @@
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
-          <t>3. u 也可以是辅音或元音。在古典时期（以及之后几个世纪），罗马人用字母 v 代表辅音和元音，而 u 只是它的圆角版本。</t>
+          <t>1. k只出现在少数几个单词中，大多是外来语。y和z出现在名字转写以及其他希腊语借词中。</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4377,7 @@
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
-          <t>不翻了……</t>
+          <t>k只在少数单词中出现，其中大多是外来词汇。y和z出现在名字转写以及其他希腊语借词中。</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4392,7 @@
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Some modern editors use u for both consonant and vowel, while others maintain the convention of using v for the consonant and u for the vowel.</t>
+          <t>2. i can be either a consonant or a vowel. In some Latin texts, j is used as the sign of consonantal i. but in this book i is used for both the consonant and the vowel.</t>
         </is>
       </c>
     </row>
@@ -4263,44 +4407,44 @@
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
-          <t>一些现代编辑用u表示辅音和元音，而另一些则保留了v表示辅音，u表示元音的习惯。</t>
+          <t>2． i既可以是辅音，也可以是元音。在一些拉丁文本中，j用来表示辅音i，但本书中，i既用于辅音又用于元音。</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
-      <c r="C246" t="inlineStr"/>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>8.3 同上</t>
+          <t>2.i既可以是辅音也可以是元音。在一些拉丁文中用j来表示辅音i，但在本书中i用于辅音也用于元音。</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A247" t="inlineStr"/>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>而现在一些编辑则用u表辅音和元音，另一些还是保留了v表辅音、u表元音的习惯。</t>
+          <t xml:space="preserve">3. u also can be either a consonant or a vowel. In the classical period (and for several centuries afterward), Romans used the letter v to represent both the consonant and the vowel, and u was simply a rounded version of this letter. </t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -4308,7 +4452,7 @@
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
-          <t>This latter convention is the one followed in this book.</t>
+          <t>3. u 也可以是辅音或元音。在古典时期（以及之后几个世纪），罗马人用字母 v 代表辅音和元音，而 u 只是它的圆角版本。</t>
         </is>
       </c>
     </row>
@@ -4327,14 +4471,14 @@
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>本书遵循后一种惯例。</t>
+          <t>不翻了……</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -4342,18 +4486,26 @@
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>本书沿用后者。</t>
+          <t>Some modern editors use u for both consonant and vowel, while others maintain the convention of using v for the consonant and u for the vowel.</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr"/>
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr"/>
-      <c r="C251" t="inlineStr"/>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. The capital letter C, in origin a form of the Greek letter gamma (Γ), originally was used by the Etruscans, who did not distinguish between the sounds of English hard g and hard c. </t>
+          <t>一些现代编辑用u表示辅音和元音，而另一些则保留了v表示辅音，u表示元音的习惯。</t>
         </is>
       </c>
     </row>
@@ -4364,15 +4516,11 @@
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. 大写字母C起源于希腊字母 gamma（Γ）的一种形式。伊特鲁里亚人最先使用，他们并不区分英语中硬 g 和硬 c 的发音。 </t>
+          <t>而现在一些编辑则用u表辅音和元音，另一些还是保留了v表辅音、u表元音的习惯。</t>
         </is>
       </c>
     </row>
@@ -4387,37 +4535,37 @@
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>4. 大写的C源于希腊字母（Γ）的大写形式，由不区分英语中硬g（hard g）和硬c（hard c）的伊特鲁里亚人最先使用。</t>
+          <t>8.2 改到这里</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>*加注释 以及后面几行应该不需要修改？</t>
+          <t>This latter convention is the one followed in this book.</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr"/>
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Even after Latin developed a separate new letter to represent hard g, capital C continued to represent hard g in abbreviations for certain first names (e.g., C. = Gaius).</t>
+          <t>本书遵循后一种惯例。</t>
         </is>
       </c>
     </row>
@@ -4436,29 +4584,25 @@
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>即使拉丁语后来发展了单独的新字母来表示硬 g，大写字母 C依然在某些名字缩写中表硬 g（如 C. = Gaius）。</t>
+          <t>本书沿用后者。</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A257" t="inlineStr"/>
       <c r="B257" t="inlineStr"/>
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>5.拉丁语的词源学，以及拉丁词汇在罗曼语族中的演变、发展</t>
+          <t xml:space="preserve">4. The capital letter C, in origin a form of the Greek letter gamma (Γ), originally was used by the Etruscans, who did not distinguish between the sounds of English hard g and hard c. </t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -4466,7 +4610,7 @@
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
-          <t>8.3 同上</t>
+          <t xml:space="preserve">4. 大写字母C起源于希腊字母 gamma（Γ）的一种形式。伊特鲁里亚人最先使用，他们并不区分英语中硬 g 和硬 c 的发音。 </t>
         </is>
       </c>
     </row>
@@ -4477,56 +4621,64 @@
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
-      <c r="C259" t="inlineStr"/>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>虽然后来拉丁语使用了新字母来表示硬g，但大写字母C仍在部分名称缩写中表示硬 g（如 C. = Gaius）。</t>
+          <t>4. 大写的C源于希腊字母（Γ）的大写形式，由不区分英语中硬g（hard g）和硬c（hard c）的伊特鲁里亚人最先使用。</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr"/>
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr"/>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Consonants </t>
+          <t>*加注释 以及后面几行应该不需要修改？</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
-      <c r="C261" t="inlineStr"/>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">辅音 </t>
+          <t>Even after Latin developed a separate new letter to represent hard g, capital C continued to represent hard g in abbreviations for certain first names (e.g., C. = Gaius).</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr"/>
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr"/>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Latin consonants are generally identical in pronunciation with their English equivalents. Exceptions are: </t>
+          <t>即使拉丁语后来发展了单独的新字母来表示硬 g，大写字母 C依然在某些名字缩写中表硬 g（如 C. = Gaius）。</t>
         </is>
       </c>
     </row>
@@ -4537,26 +4689,30 @@
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
-      <c r="C263" t="inlineStr"/>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>拉丁语辅音通常与英语相对应的辅音发音相同。除了：</t>
+          <t>虽然后来拉丁语使用了新字母来表示硬g，但大写字母C仍在部分名称缩写中表示硬 g（如 C. = Gaius）。</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr"/>
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr"/>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">b as b, but bs as the ps of taps; bt as the pt of apt </t>
+          <t>Alphabet</t>
         </is>
       </c>
     </row>
@@ -4571,22 +4727,22 @@
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
-          <t>b读作b，但bs读作taps的ps；b读作apt的pt</t>
+          <t>8.2 改到这里</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr"/>
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr"/>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">c as the c of cart (hard c) </t>
+          <t xml:space="preserve">Consonants </t>
         </is>
       </c>
     </row>
@@ -4597,26 +4753,30 @@
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
-      <c r="C267" t="inlineStr"/>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
-          <t>c 读作cart 的 c（硬 c）；</t>
+          <t xml:space="preserve">辅音 </t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr"/>
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr"/>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">g as the g of get (hard g) </t>
+          <t xml:space="preserve">The Latin consonants are generally identical in pronunciation with their English equivalents. Exceptions are: </t>
         </is>
       </c>
     </row>
@@ -4627,64 +4787,56 @@
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
-      <c r="C269" t="inlineStr"/>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
-          <t>g读作get 的 g（硬 g）；</t>
+          <t>拉丁语辅音通常与英语相对应的辅音发音相同。除了：</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr"/>
       <c r="B270" t="inlineStr"/>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
-          <t>h as the h of hat</t>
+          <t xml:space="preserve">b as b, but bs as the ps of taps; bt as the pt of apt </t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>h读作hat的h</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>【截图序号：33】</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr"/>
+          <t>【正文译文】</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBSERVATION </t>
+          <t>b读作b，但bs读作taps的ps；b读作apt的pt</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>h读作hat的h</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>【截图序号：33】</t>
-        </is>
-      </c>
+      <c r="A272" t="inlineStr"/>
+      <c r="B272" t="inlineStr"/>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
-          <t>h represents the expelling of air (aspiration).</t>
+          <t xml:space="preserve">c as the c of cart (hard c) </t>
         </is>
       </c>
     </row>
@@ -4694,35 +4846,27 @@
           <t>【正文译文】</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>【截图序号：33】</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr"/>
+      <c r="B273" t="inlineStr"/>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>h代表排出气体（即送气音）。</t>
+          <t>c 读作cart 的 c（硬 c）；</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>h读作hat的h</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>【截图序号：33】</t>
-        </is>
-      </c>
+      <c r="A274" t="inlineStr"/>
+      <c r="B274" t="inlineStr"/>
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">i, as consonant, as the y of yawn </t>
+          <t xml:space="preserve">g as the g of get (hard g) </t>
         </is>
       </c>
     </row>
@@ -4732,151 +4876,167 @@
           <t>【正文译文】</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>【截图序号：33】</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr"/>
+      <c r="B275" t="inlineStr"/>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>i作辅音时，同yawn 的 y</t>
+          <t>g读作get 的 g（硬 g）；</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>h读作hat的h</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>【截图序号：33】</t>
-        </is>
-      </c>
+      <c r="A276" t="inlineStr"/>
+      <c r="B276" t="inlineStr"/>
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>1. i is consonantal at the beginning of a word when followed by a vowel (lüno, pronounced "Yuno") and in the middle of a word when it falls between vowels (biiugis, pronounced "biyugis").</t>
+          <t>h as the h of hat</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
-      <c r="C277" t="inlineStr"/>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>8.2 改到这里</t>
+          <t>h读作hat的h</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>【批注】</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr"/>
+          <t>【原书脚注原文】</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBSERVATION </t>
+        </is>
+      </c>
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>8.3 同上</t>
+          <t>【原书脚注译文】</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr"/>
+          <t>【原书脚注原文】</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBSERVATION </t>
+        </is>
+      </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>1. i 在词首后跟元音时为辅音（Iūnō，读作 "Yūnō"），在词中且位于两元音之间时为辅音（biiugis，读作 "biyugis"）。</t>
+          <t>h represents the expelling of air (aspiration).</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr"/>
+          <t>【原书脚注原文】</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBSERVATION </t>
+        </is>
+      </c>
       <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>i may also be consonantal in the middle of a compound (that is, a word made with a root word and a prefix (iniustus [&lt; in- + iustus], pronounced "in-yustus").</t>
+          <t>h代表排出气体（即送气音）。</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr"/>
+          <t>【原书脚注原文】</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBSERVATION </t>
+        </is>
+      </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>i 在复合词中时也可能是辅音（即词根和前缀组成的词（iniustus [&lt; in- + iustus]，读作 "in-yustus"）。</t>
+          <t xml:space="preserve">i, as consonant, as the y of yawn </t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr"/>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+          <t>【原书脚注原文】</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBSERVATION </t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2. An exception to this rule occurs in certain words borrowed from Greek, in which an initial i is pronounced as a vowel (iambus, pronounced "i-ambus").</t>
+          <t>i作辅音时，同yawn 的 y</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr"/>
+          <t>【原书脚注原文】</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OBSERVATION </t>
+        </is>
+      </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2. 希腊语中借用的某些单词除外，它们中的首字母 i 作元音（iambus，读作 "i-ambus"）。</t>
+          <t>1. i is consonantal at the beginning of a word when followed by a vowel (lüno, pronounced "Yuno") and in the middle of a word when it falls between vowels (biiugis, pronounced "biyugis").</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -4884,7 +5044,7 @@
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">n as n, but nc as the nk of bank; ng as the ng of hang </t>
+          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
         </is>
       </c>
     </row>
@@ -4899,48 +5059,48 @@
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr">
         <is>
-          <t>n读作n，但 nc读作bank 的 nk；ng读作hang 的 ng，</t>
+          <t>8.2 改到这里</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
-          <t>qu as the qu of quit</t>
+          <t>1. i 在词首后跟元音时为辅音（Iūnō，读作 "Yūnō"），在词中且位于两元音之间时为辅音（biiugis，读作 "biyugis"）。</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">3. There are, of course, variations in usage and style from author to author and from the beginning of this period to the end. </t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
-      <c r="C287" t="inlineStr"/>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
-          <t>qu读作quit 的 qu</t>
+          <t>i may also be consonantal in the middle of a compound (that is, a word made with a root word and a prefix (iniustus [&lt; in- + iustus], pronounced "in-yustus").</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -4948,29 +5108,33 @@
       <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
-          <t>序号37，页数5（拆分：？，？）（机翻：？，？）（人翻：？，？）（第一次润色（按句）：？，？）（第一次校对：？，？）（第二次润色（按意群）：？，？）（第二次校对：？，？）（终润（按段落）：？，？）（终校：？，？）（附加评论/修改建议：？，？）（排版/美化：？，？）（美化后期再做）</t>
+          <t>i 在复合词中时也可能是辅音（即词根和前缀组成的词（iniustus [&lt; in- + iustus]，读作 "in-yustus"）。</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
+          <t xml:space="preserve">3. There are, of course, variations in usage and style from author to author and from the beginning of this period to the end. </t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
-      <c r="C289" t="inlineStr"/>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>2. An exception to this rule occurs in certain words borrowed from Greek, in which an initial i is pronounced as a vowel (iambus, pronounced "i-ambus").</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -4978,26 +5142,22 @@
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Although qu is written with a-u.this u is the consonantal u (v).This spelling convention is also used in the combinations su and gu,which in some Latin words are pronounced as the su of persuade and the gu of anguish.</t>
+          <t>2. 希腊语中借用的某些单词除外，它们中的首字母 i 作元音（iambus，读作 "i-ambus"）。</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">3. There are, of course, variations in usage and style from author to author and from the beginning of this period to the end. </t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
-          <t>虽然qu是用一个 -u写的。这个u是辅音u (v)。这种拼写习惯也用于su和gu的组合，在一些拉丁单词中，su的发音是“persuade”的su, gu的发音是“anguish”的gu。</t>
+          <t xml:space="preserve">n as n, but nc as the nk of bank; ng as the ng of hang </t>
         </is>
       </c>
     </row>
@@ -5008,26 +5168,34 @@
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
-      <c r="C292" t="inlineStr"/>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
-          <t>虽然写作qu，但其中的u（v）是个辅音。这是一种拼写习惯，也用于su和gu之中，在拉丁单词中这两种组合分别发persuade和anguish中对应字母组合的音。</t>
+          <t>n读作n，但 nc读作bank 的 nk；ng读作hang 的 ng，</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
+          <t xml:space="preserve">3. There are, of course, variations in usage and style from author to author and from the beginning of this period to the end. </t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
-      <c r="C293" t="inlineStr"/>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
-          <t>su and gu when so pronounced count as single consonants. That is, although they are spelled with two letters, they represent a single sound in Latin.</t>
+          <t>qu as the qu of quit</t>
         </is>
       </c>
     </row>
@@ -5038,22 +5206,18 @@
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>“su”和 “gu "在发音时被视为单辅音。也就是说，虽然它们是用两个字母拼写的，但在拉丁语中只代表一个音。</t>
+          <t>qu读作quit 的 qu</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【分工】</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -5061,25 +5225,29 @@
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
-          <t>它们被发作单辅音，即虽然有两个字母，但在拉丁语中只对应一个音。</t>
+          <t>序号37，页数5（拆分：？，？）（机翻：？，？）（人翻：？，？）（第一次润色（按句）：？，？）（第一次校对：？，？）（第二次润色（按意群）：？，？）（第二次校对：？，？）（终润（按段落）：？，？）（终校：？，？）（附加评论/修改建议：？，？）（排版/美化：？，？）（美化后期再做）</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr"/>
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>r as a rolled r</t>
+          <t>OBSERVATION</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">3. There are, of course, variations in usage and style from author to author and from the beginning of this period to the end. </t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -5087,18 +5255,26 @@
       <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
-          <t>r读作卷舌的r；</t>
+          <t xml:space="preserve"> Although qu is written with a-u.this u is the consonantal u (v).This spelling convention is also used in the combinations su and gu,which in some Latin words are pronounced as the su of persuade and the gu of anguish.</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr"/>
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr"/>
-      <c r="C298" t="inlineStr"/>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve"> s as the s of serpent </t>
+          <t>虽然qu是用一个 -u写的。这个u是辅音u (v)。这种拼写习惯也用于su和gu的组合，在一些拉丁单词中，su的发音是“persuade”的su, gu的发音是“anguish”的gu。</t>
         </is>
       </c>
     </row>
@@ -5113,14 +5289,14 @@
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve"> s通常是一个齿擦音，就像在“serpent”中的s（永远不要发成z）；</t>
+          <t>虽然写作qu，但其中的u（v）是个辅音。这是一种拼写习惯，也用于su和gu之中，在拉丁单词中这两种组合分别发persuade和anguish中对应字母组合的音。</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t xml:space="preserve">3. There are, of course, variations in usage and style from author to author and from the beginning of this period to the end. </t>
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -5128,46 +5304,42 @@
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve"> s读作serpent中的s</t>
+          <t>su and gu when so pronounced count as single consonants. That is, although they are spelled with two letters, they represent a single sound in Latin.</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr"/>
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr"/>
-      <c r="C301" t="inlineStr"/>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v(consonantal u)as the w of wet </t>
+          <t>“su”和 “gu "在发音时被视为单辅音。也就是说，虽然它们是用两个字母拼写的，但在拉丁语中只代表一个音。</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A302" t="inlineStr"/>
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr"/>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>v（辅音u）读作“wet“中的w</t>
-        </is>
-      </c>
+      <c r="E302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr"/>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr"/>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">x as the x of axe </t>
-        </is>
-      </c>
+      <c r="E303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -5180,85 +5352,89 @@
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
-          <t>x被当作一个双辅音，（等于ks），发音像axe中的x；z被当作一个双辅音，（等于dz）。发音像gadzooks中的dz</t>
+          <t>它们被发作单辅音，即虽然有两个字母，但在拉丁语中只对应一个音。</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A305" t="inlineStr"/>
       <c r="B305" t="inlineStr"/>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
-          <t>x读作axe中的x</t>
+          <t>r as a rolled r</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr"/>
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr"/>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
-          <t>z as the dz of gadzooks</t>
+          <t>r读作卷舌的r；</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A307" t="inlineStr"/>
       <c r="B307" t="inlineStr"/>
-      <c r="C307" t="inlineStr"/>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
-          <t>z读作gadzooks中的dz</t>
+          <t xml:space="preserve"> s as the s of serpent </t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr"/>
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr"/>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve"> OBSERVATION</t>
+          <t xml:space="preserve"> s通常是一个齿擦音，就像在“serpent”中的s（永远不要发成z）；</t>
         </is>
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr"/>
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr"/>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve"> z is a consonant representing the Greek zeta(Z).which represented the sound of two consonants in Greek </t>
+          <t xml:space="preserve"> s读作serpent中的s</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A310" t="inlineStr"/>
       <c r="B310" t="inlineStr"/>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>z是用来表示希腊字母zeta(z)的辅音字母。它在希腊语中是一个双辅音。</t>
+          <t xml:space="preserve">v(consonantal u)as the w of wet </t>
         </is>
       </c>
     </row>
@@ -5269,11 +5445,15 @@
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
-      <c r="C311" t="inlineStr"/>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>z用来表示希腊字母zeta(Z)的辅音字母，在希腊语中表示两个辅音。</t>
+          <t>v（辅音u）读作“wet“中的w</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5464,7 @@
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">ch as the ch of character </t>
+          <t xml:space="preserve">x as the x of axe </t>
         </is>
       </c>
     </row>
@@ -5295,11 +5475,15 @@
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
-      <c r="C313" t="inlineStr"/>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>ch是character的ch, p是people的p, t是tea的t</t>
+          <t>x被当作一个双辅音，（等于ks），发音像axe中的x；z被当作一个双辅音，（等于dz）。发音像gadzooks中的dz</t>
         </is>
       </c>
     </row>
@@ -5314,18 +5498,22 @@
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>ch读作character的ch</t>
+          <t>x读作axe中的x</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr"/>
       <c r="B315" t="inlineStr"/>
-      <c r="C315" t="inlineStr"/>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>ph as the p of people</t>
+          <t>z as the dz of gadzooks</t>
         </is>
       </c>
     </row>
@@ -5340,44 +5528,52 @@
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>p读作people的p</t>
+          <t>z读作gadzooks中的dz</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr"/>
       <c r="B317" t="inlineStr"/>
-      <c r="C317" t="inlineStr"/>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve"> th as the t of tea </t>
+          <t xml:space="preserve"> OBSERVATION</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A318" t="inlineStr"/>
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve"> t是tea的t</t>
+          <t xml:space="preserve"> z is a consonant representing the Greek zeta(Z).which represented the sound of two consonants in Greek </t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr"/>
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr"/>
-      <c r="C319" t="inlineStr"/>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ch,ph,and th represent sounds introduced into Latin from Greek.Greek distinguished between the unaspirated and aspirated consonants c and ch,p and ph.and t and th.</t>
+          <t>z是用来表示希腊字母zeta(z)的辅音字母。它在希腊语中是一个双辅音。</t>
         </is>
       </c>
     </row>
@@ -5392,29 +5588,29 @@
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>希腊语传入拉丁语的发音使用ch,ph和th表示，因为在希腊语中，分别使用c和ch,p和ph, t和th来表达不送气辅音和送气辅音。</t>
+          <t>z用来表示希腊字母zeta(Z)的辅音字母，在希腊语中表示两个辅音。</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>【正文原文】</t>
-        </is>
-      </c>
+      <c r="A321" t="inlineStr"/>
       <c r="B321" t="inlineStr"/>
-      <c r="C321" t="inlineStr"/>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
-          <t>The -h represents the puff of air(aspiration)that is emitted after the consonant sound is made.</t>
+          <t xml:space="preserve">ch as the ch of character </t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
@@ -5422,7 +5618,7 @@
       <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
-          <t>8.3 同上</t>
+          <t>ch是character的ch, p是people的p, t是tea的t</t>
         </is>
       </c>
     </row>
@@ -5433,26 +5629,26 @@
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
-      <c r="C323" t="inlineStr"/>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D323" t="inlineStr"/>
       <c r="E323" t="inlineStr">
         <is>
-          <t>其中的-h表示在发出辅音后送出一股空气（即送气）。</t>
+          <t>ch读作character的ch</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>【正文原文】</t>
-        </is>
-      </c>
+      <c r="A324" t="inlineStr"/>
       <c r="B324" t="inlineStr"/>
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>This distinction between unaspirated and aspirated consonants is also made in modern French and in other Romance languages,although not in English:the English pronunciation of c,p.and t always includes aspiration.</t>
+          <t>ph as the p of people</t>
         </is>
       </c>
     </row>
@@ -5463,26 +5659,26 @@
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
-      <c r="C325" t="inlineStr"/>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
-          <t>现代法语和其他罗曼语中也有这种不送气和送气辅音的区别，但英语中没有，因为英语中c,p,t发音总是送气的。</t>
+          <t>p读作people的p</t>
         </is>
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>【正文原文】</t>
-        </is>
-      </c>
+      <c r="A326" t="inlineStr"/>
       <c r="B326" t="inlineStr"/>
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr"/>
       <c r="E326" t="inlineStr">
         <is>
-          <t>In order to distinguish in Latin words ph and th from p and t,it has become conventional to pronounce ph as the ph of philosophy and th as the th of theater. The pronunciations given above(people,tea)are to be preferred.</t>
+          <t xml:space="preserve"> th as the t of tea </t>
         </is>
       </c>
     </row>
@@ -5493,11 +5689,15 @@
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
-      <c r="C327" t="inlineStr"/>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>人们为了区分拉丁语单词中的ph,th与p,t，习惯把ph读成philosophy的ph，把th读成theater的th，不过这里我们应首选tea的t及people的p。</t>
+          <t xml:space="preserve"> t是tea的t</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5708,7 @@
       <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vowels </t>
+          <t xml:space="preserve"> ch,ph,and th represent sounds introduced into Latin from Greek.Greek distinguished between the unaspirated and aspirated consonants c and ch,p and ph.and t and th.</t>
         </is>
       </c>
     </row>
@@ -5519,22 +5719,30 @@
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
-      <c r="C329" t="inlineStr"/>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D329" t="inlineStr"/>
       <c r="E329" t="inlineStr">
         <is>
-          <t>元音</t>
+          <t>希腊语传入拉丁语的发音使用ch,ph和th表示，因为在希腊语中，分别使用c和ch,p和ph, t和th来表达不送气辅音和送气辅音。</t>
         </is>
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr"/>
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr"/>
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr"/>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Latin has two sets of five vowels:</t>
+          <t>The -h represents the puff of air(aspiration)that is emitted after the consonant sound is made.</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5757,7 @@
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">拉丁文有两套五元音: </t>
+          <t>8.2 改到这里</t>
         </is>
       </c>
     </row>
@@ -5564,14 +5772,14 @@
       <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
-          <t>【表格】</t>
+          <t>其中的-h表示在发出辅音后送出一股空气（即送气）。</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -5579,62 +5787,90 @@
       <c r="D333" t="inlineStr"/>
       <c r="E333" t="inlineStr">
         <is>
-          <t>短元音    长元音</t>
+          <t>This distinction between unaspirated and aspirated consonants is also made in modern French and in other Romance languages,although not in English:the English pronunciation of c,p.and t always includes aspiration.</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr"/>
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr"/>
-      <c r="C334" t="inlineStr"/>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
-          <t>a                 ā</t>
+          <t>现代法语和其他罗曼语中也有这种不送气和送气辅音的区别，但英语中没有，因为英语中c,p,t发音总是送气的。</t>
         </is>
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr"/>
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr"/>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>e                 ē</t>
+          <t>In order to distinguish in Latin words ph and th from p and t,it has become conventional to pronounce ph as the ph of philosophy and th as the th of theater. The pronunciations given above(people,tea)are to be preferred.</t>
         </is>
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr"/>
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr"/>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>i                   ī</t>
+          <t>人们为了区分拉丁语单词中的ph,th与p,t，习惯把ph读成philosophy的ph，把th读成theater的th，不过这里我们应首选tea的t及people的p。</t>
         </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr"/>
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr"/>
-      <c r="C337" t="inlineStr"/>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">o                 ō </t>
+          <t xml:space="preserve">Vowels </t>
         </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr"/>
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr"/>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
-          <t>u                 ū</t>
+          <t>元音</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5881,7 @@
       <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.Vowels have both quantity and quality.</t>
+          <t xml:space="preserve"> Latin has two sets of five vowels:</t>
         </is>
       </c>
     </row>
@@ -5656,22 +5892,30 @@
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
-      <c r="C340" t="inlineStr"/>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>1.元音有音量和音质两个属性</t>
+          <t xml:space="preserve">拉丁文有两套五元音: </t>
         </is>
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr"/>
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Ouantity refers to the length of a vowel.</t>
+          <t>【表格】</t>
         </is>
       </c>
     </row>
@@ -5686,104 +5930,96 @@
       <c r="D342" t="inlineStr"/>
       <c r="E342" t="inlineStr">
         <is>
-          <t>音量指元音长度。</t>
+          <t>【表格序号：1】</t>
         </is>
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr"/>
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr"/>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>A Latin vowel marked with a macron or long mark is long and takes approximately twice as long to pronounce as a short vowel.Vowels not so marked are short.</t>
+          <t>短元音    长元音</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A344" t="inlineStr"/>
       <c r="B344" t="inlineStr"/>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>一个带有长标记（-）的拉丁元音是长元音（发音的时间大约是短元音的两倍），没有这样标记的是短元音。</t>
+          <t>a                 ā</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A345" t="inlineStr"/>
       <c r="B345" t="inlineStr"/>
-      <c r="C345" t="inlineStr"/>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>拉丁元音的长元音（大约比短元音长一倍）标着长音符( ¯ )，短元音则没有。</t>
+          <t>e                 ē</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A346" t="inlineStr"/>
       <c r="B346" t="inlineStr"/>
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>带有长音符（-）的拉丁元音是长元音（发音时间约为短元音的两倍），没有则为短元音。</t>
+          <t>i                   ī</t>
         </is>
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>【正文原文】</t>
-        </is>
-      </c>
+      <c r="A347" t="inlineStr"/>
       <c r="B347" t="inlineStr"/>
       <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr"/>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Quality refers to the way a vowel is pronounced.For example,and are the same in quantity but different in quality.</t>
+          <t xml:space="preserve">o                 ō </t>
         </is>
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A348" t="inlineStr"/>
       <c r="B348" t="inlineStr"/>
       <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>音质指元音的发音方式。例如，ā 和 ō 两者音量相同，但音质不同。</t>
+          <t>u                 ū</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr"/>
       <c r="B349" t="inlineStr"/>
-      <c r="C349" t="inlineStr"/>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2.A vowel in a Latin word is either long or short by nature.It is important to realize that,for example,a and long a are two different vowels,even if they are closely related.</t>
+          <t xml:space="preserve"> 1.Vowels have both quantity and quality.</t>
         </is>
       </c>
     </row>
@@ -5798,29 +6034,33 @@
       <c r="D350" t="inlineStr"/>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2.拉丁语单词中的元音不是自然长就是自然短。重要的是要认识到，如a和长ā是即便是紧密相关的，也是两个不同的元音。</t>
+          <t>1.元音有音量和音质两个属性</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
-      <c r="C351" t="inlineStr"/>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D351" t="inlineStr"/>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2.拉丁语单词中的元音不是自然长就是自然短（long or short by nature），但要意识到，比如a和ā虽极为相似，却是两个不同的元音。</t>
+          <t>Ouantity refers to the length of a vowel.</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>【译者注释】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -5828,33 +6068,41 @@
       <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
-          <t>注释：2. 一些留存的文本，如西塞罗的演讲，表明了古典拉丁语既有书面的也有口头的。</t>
+          <t>音量指元音长度。</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
-      <c r="C353" t="inlineStr"/>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>8.3 同上</t>
+          <t>A Latin vowel marked with a macron or long mark is long and takes approximately twice as long to pronounce as a short vowel.Vowels not so marked are short.</t>
         </is>
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="inlineStr"/>
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr"/>
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>3.Differences in vowel length often convey significant differences in meaning.For example, the word alium (with a short a-)means"another man";the word ālium (with a long -means "garlic."</t>
+          <t>一个带有长标记（-）的拉丁元音是长元音（发音的时间大约是短元音的两倍），没有这样标记的是短元音。</t>
         </is>
       </c>
     </row>
@@ -5865,11 +6113,15 @@
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
-      <c r="C355" t="inlineStr"/>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>3.元音长度的不同往往传达了意义上的显著差异。例如，单词alium(以短的a-开头)表示“另一个人”;单词alium(以长-开头)表示“大蒜”。</t>
+          <t>拉丁元音的长元音（大约比短元音长一倍）标着长音符( ¯ )，短元音则没有。</t>
         </is>
       </c>
     </row>
@@ -5884,48 +6136,52 @@
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>3.元音长度不同往往含义大不同，比如单词alium(a打头)表示“另一个人”；单词ālium(ā打头)却表示“大蒜”。</t>
+          <t>带有长音符（-）的拉丁元音是长元音（发音时间约为短元音的两倍），没有则为短元音。</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
-      <c r="C357" t="inlineStr"/>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D357" t="inlineStr"/>
       <c r="E357" t="inlineStr">
         <is>
-          <t>序号38，页数6（拆分：？，？）（机翻：？，？）（人翻：？，？）（第一次润色（按句）：？，？）（第一次校对：？，？）（第二次润色（按意群）：？，？）（第二次校对：？，？）（终润（按段落）：？，？）（终校：？，？）（附加评论/修改建议：？，？）（排版/美化：？，？）（美化后期再做）</t>
+          <t>Quality refers to the way a vowel is pronounced.For example,and are the same in quantity but different in quality.</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr"/>
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B358" t="inlineStr"/>
       <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
-          <t>A MACRON ON A LONG VOWEL SHOULD BE CONSIDERED PART OF THE SPELLING OF A LATIN WORD. WHEN LEARNING NEW VOCABULARY,MEMORIZE ALL MACRONS AND AL- WAYS WRITE THEM ON LONG VOWELS. 5</t>
+          <t>音质指元音的发音方式。例如，ā 和 ō 两者音量相同，但音质不同。</t>
         </is>
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A359" t="inlineStr"/>
       <c r="B359" t="inlineStr"/>
       <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr"/>
       <c r="E359" t="inlineStr">
         <is>
-          <t>长元音（Long vowel）上的长音符（Macron）应认为是拉丁语单词拼写的一部分。学习新单词时，要注意识记长音符，并总是将它们标注在长元音上。5</t>
+          <t>2.A vowel in a Latin word is either long or short by nature.It is important to realize that,for example,a and long a are two different vowels,even if they are closely related.</t>
         </is>
       </c>
     </row>
@@ -5936,22 +6192,30 @@
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
-      <c r="C360" t="inlineStr"/>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D360" t="inlineStr"/>
       <c r="E360" t="inlineStr">
         <is>
-          <t>谨记，长音符也是单词的一部分，学习新单词时要记住并标注长音符。</t>
+          <t>2.拉丁语单词中的元音不是自然长就是自然短。重要的是要认识到，如a和长ā是即便是紧密相关的，也是两个不同的元音。</t>
         </is>
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr"/>
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr"/>
       <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
-          <t xml:space="preserve">The vowels are pronounced as follows: </t>
+          <t>注释：2. 一些留存的文本，如西塞罗的演讲，表明了古典拉丁语既有书面的也有口头的。</t>
         </is>
       </c>
     </row>
@@ -5966,44 +6230,48 @@
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
-          <t>元音发音规则如下:</t>
+          <t>8.2 改到这里</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr"/>
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr"/>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr"/>
       <c r="E363" t="inlineStr">
         <is>
-          <t>a as the a of alert or the u of cup</t>
+          <t>2.拉丁语单词中的元音不是自然长就是自然短（long or short by nature），但要意识到，比如a和ā虽极为相似，却是两个不同的元音。</t>
         </is>
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A364" t="inlineStr"/>
       <c r="B364" t="inlineStr"/>
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr"/>
       <c r="E364" t="inlineStr">
         <is>
-          <t>a读作 alert 的 a或者cup的u；</t>
+          <t>3.Differences in vowel length often convey significant differences in meaning.For example, the word alium (with a short a-)means"another man";the word ālium (with a long -means "garlic."</t>
         </is>
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr"/>
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr"/>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr"/>
       <c r="E365" t="inlineStr">
         <is>
-          <t>ā as the a of father</t>
+          <t>3.元音长度的不同往往传达了意义上的显著差异。例如，单词alium(以短的a-开头)表示“另一个人”;单词alium(以长-开头)表示“大蒜”。</t>
         </is>
       </c>
     </row>
@@ -6018,25 +6286,29 @@
       <c r="D366" t="inlineStr"/>
       <c r="E366" t="inlineStr">
         <is>
-          <t>ā读作father的a</t>
+          <t>3.元音长度不同往往含义大不同，比如单词alium(a打头)表示“另一个人”；单词ālium(ā打头)却表示“大蒜”。</t>
         </is>
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr"/>
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>【分工】</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr"/>
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve"> e as the e of pet </t>
+          <t>序号38，页数6（拆分：？，？）（机翻：？，？）（人翻：？，？）（第一次润色（按句）：？，？）（第一次校对：？，？）（第二次润色（按意群）：？，？）（第二次校对：？，？）（终润（按段落）：？，？）（终校：？，？）（附加评论/修改建议：？，？）（排版/美化：？，？）（美化后期再做）</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -6044,18 +6316,26 @@
       <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
-          <t>e读作pet的e</t>
+          <t>A MACRON ON A LONG VOWEL SHOULD BE CONSIDERED PART OF THE SPELLING OF A LATIN WORD. WHEN LEARNING NEW VOCABULARY,MEMORIZE ALL MACRONS AND AL- WAYS WRITE THEM ON LONG VOWELS. 5</t>
         </is>
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="inlineStr"/>
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr"/>
-      <c r="C369" t="inlineStr"/>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D369" t="inlineStr"/>
       <c r="E369" t="inlineStr">
         <is>
-          <t>ē as the a of fate</t>
+          <t>长元音（Long vowel）上的长音符（Macron）应认为是拉丁语单词拼写的一部分。学习新单词时，要注意识记长音符，并总是将它们标注在长元音上。5</t>
         </is>
       </c>
     </row>
@@ -6070,46 +6350,38 @@
       <c r="D370" t="inlineStr"/>
       <c r="E370" t="inlineStr">
         <is>
-          <t>ē读作 fate的a</t>
+          <t>谨记，长音符也是单词的一部分，学习新单词时要记住并标注长音符。</t>
         </is>
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr"/>
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr"/>
       <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr"/>
       <c r="E371" t="inlineStr">
         <is>
-          <t xml:space="preserve"> i as the i of fit</t>
+          <t xml:space="preserve">The vowels are pronounced as follows: </t>
         </is>
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A372" t="inlineStr"/>
       <c r="B372" t="inlineStr"/>
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>i读作fit的i</t>
-        </is>
-      </c>
+      <c r="E372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr"/>
       <c r="B373" t="inlineStr"/>
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr"/>
-      <c r="E373" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ī as the ee of feet </t>
-        </is>
-      </c>
+      <c r="E373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -6122,7 +6394,7 @@
       <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
-          <t xml:space="preserve">ī读作 feet的ee </t>
+          <t>元音发音规则如下:</t>
         </is>
       </c>
     </row>
@@ -6133,7 +6405,7 @@
       <c r="D375" t="inlineStr"/>
       <c r="E375" t="inlineStr">
         <is>
-          <t xml:space="preserve">o as the o of soft or the au of caught </t>
+          <t>a as the a of alert or the u of cup</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6420,7 @@
       <c r="D376" t="inlineStr"/>
       <c r="E376" t="inlineStr">
         <is>
-          <t>o读作soft的o或caught的au</t>
+          <t>a读作 alert 的 a或者cup的u；</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6431,7 @@
       <c r="D377" t="inlineStr"/>
       <c r="E377" t="inlineStr">
         <is>
-          <t xml:space="preserve">ō as the o of hope </t>
+          <t>ā as the a of father</t>
         </is>
       </c>
     </row>
@@ -6174,18 +6446,22 @@
       <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
-          <t xml:space="preserve">ō 读作 hope的o </t>
+          <t>ā读作father的a</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr"/>
       <c r="B379" t="inlineStr"/>
-      <c r="C379" t="inlineStr"/>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
-          <t xml:space="preserve">u as the u of put </t>
+          <t xml:space="preserve"> e as the e of pet </t>
         </is>
       </c>
     </row>
@@ -6200,7 +6476,7 @@
       <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
-          <t xml:space="preserve">u读作put的u </t>
+          <t>e读作pet的e</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6487,7 @@
       <c r="D381" t="inlineStr"/>
       <c r="E381" t="inlineStr">
         <is>
-          <t xml:space="preserve">ū as the oo of fool </t>
+          <t>ē as the a of fate</t>
         </is>
       </c>
     </row>
@@ -6222,11 +6498,15 @@
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
-      <c r="C382" t="inlineStr"/>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" t="inlineStr">
         <is>
-          <t xml:space="preserve">ū 读作fool的oo </t>
+          <t>ē读作 fate的a</t>
         </is>
       </c>
     </row>
@@ -6237,33 +6517,33 @@
       <c r="D383" t="inlineStr"/>
       <c r="E383" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBSERVATIONS </t>
+          <t xml:space="preserve"> i as the i of fit</t>
         </is>
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr"/>
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr"/>
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr"/>
       <c r="E384" t="inlineStr">
         <is>
-          <t>1.a and a are very similar in quality and differ only in quantity.Care must be taken in the pronunciation of these two vowels</t>
+          <t>i读作fit的i</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A385" t="inlineStr"/>
       <c r="B385" t="inlineStr"/>
       <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr">
         <is>
-          <t>1.a和ā</t>
+          <t xml:space="preserve">ī as the ee of feet </t>
         </is>
       </c>
     </row>
@@ -6278,22 +6558,22 @@
       <c r="D386" t="inlineStr"/>
       <c r="E386" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 在音质（quality ）上很相似，只是音量（quantity）不同。{讨论：术语不确定，选取了使用最多的翻译}</t>
+          <t xml:space="preserve">ī读作 feet的ee </t>
         </is>
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A387" t="inlineStr"/>
       <c r="B387" t="inlineStr"/>
-      <c r="C387" t="inlineStr"/>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D387" t="inlineStr"/>
       <c r="E387" t="inlineStr">
         <is>
-          <t>必须仔细区分这两个元音的发音</t>
+          <t xml:space="preserve">o as the o of soft or the au of caught </t>
         </is>
       </c>
     </row>
@@ -6308,52 +6588,48 @@
       <c r="D388" t="inlineStr"/>
       <c r="E388" t="inlineStr">
         <is>
-          <t>1.a和ā 在</t>
+          <t>o读作soft的o或caught的au</t>
         </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A389" t="inlineStr"/>
       <c r="B389" t="inlineStr"/>
       <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr"/>
       <c r="E389" t="inlineStr">
         <is>
-          <t>5.拉丁语的词源学，以及拉丁词汇在罗曼语族中的演变、发展</t>
+          <t xml:space="preserve">ō as the o of hope </t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B390" t="inlineStr"/>
-      <c r="C390" t="inlineStr"/>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D390" t="inlineStr"/>
       <c r="E390" t="inlineStr">
         <is>
-          <t>8.3 同上</t>
+          <t xml:space="preserve">ō 读作 hope的o </t>
         </is>
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A391" t="inlineStr"/>
       <c r="B391" t="inlineStr"/>
       <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr">
         <is>
-          <t>音质（quality ）上几乎一致</t>
+          <t xml:space="preserve">u as the u of put </t>
         </is>
       </c>
     </row>
@@ -6368,22 +6644,22 @@
       <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr">
         <is>
-          <t>，只在</t>
+          <t xml:space="preserve">u读作put的u </t>
         </is>
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A393" t="inlineStr"/>
       <c r="B393" t="inlineStr"/>
-      <c r="C393" t="inlineStr"/>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D393" t="inlineStr"/>
       <c r="E393" t="inlineStr">
         <is>
-          <t>音量（quantity）上有所区别，</t>
+          <t xml:space="preserve">ū as the oo of fool </t>
         </is>
       </c>
     </row>
@@ -6398,33 +6674,33 @@
       <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
-          <t>发音时一定要注意区别。</t>
+          <t xml:space="preserve">ū 读作fool的oo </t>
         </is>
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr"/>
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B395" t="inlineStr"/>
       <c r="C395" t="inlineStr"/>
       <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr">
         <is>
-          <t>.All other pairs of vowels(e and e,etc.)differ both in quality and in quantity and are easier for the English speaker to differentiate.</t>
+          <t xml:space="preserve">OBSERVATIONS </t>
         </is>
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A396" t="inlineStr"/>
       <c r="B396" t="inlineStr"/>
       <c r="C396" t="inlineStr"/>
       <c r="D396" t="inlineStr"/>
       <c r="E396" t="inlineStr">
         <is>
-          <t>所有其他元音对(e和ē等)</t>
+          <t>1.a and a are very similar in quality and differ only in quantity.Care must be taken in the pronunciation of these two vowels</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6715,7 @@
       <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr">
         <is>
-          <t>在音质和音量</t>
+          <t>1.a和ā</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6730,7 @@
       <c r="D398" t="inlineStr"/>
       <c r="E398" t="inlineStr">
         <is>
-          <t>上都不同，这对英语使用者（the English speaker）来说更容易区分。</t>
+          <t xml:space="preserve"> 在音质（quality ）上很相似，只是音量（quantity）不同。{讨论：术语不确定，选取了使用最多的翻译}</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6745,7 @@
       <c r="D399" t="inlineStr"/>
       <c r="E399" t="inlineStr">
         <is>
-          <t>其他的元音对(e和ē等)在音质与音量上均不同，说英语的人更易区分它们。</t>
+          <t>必须仔细区分这两个元音的发音</t>
         </is>
       </c>
     </row>
@@ -6478,16 +6754,12 @@
       <c r="B400" t="inlineStr"/>
       <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr"/>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>2.y is a vowel representing the Greek upsilon(Y).This vowel is pronounced as a French u (a sound in between the English i and u).It may be long or short;the long vowel is pronounced twice as long as the short.</t>
-        </is>
-      </c>
+      <c r="E400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -6495,7 +6767,7 @@
       <c r="D401" t="inlineStr"/>
       <c r="E401" t="inlineStr">
         <is>
-          <t>2.y是一个表示希腊语中的upsilon(Y)的元音。它发成法语的u(介于英语i和u之间)，</t>
+          <t>Alphabet</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6782,7 @@
       <c r="D402" t="inlineStr"/>
       <c r="E402" t="inlineStr">
         <is>
-          <t>可长可短，而</t>
+          <t>8.2 改到这里</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6797,7 @@
       <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr">
         <is>
-          <t>长元音的发音是短元音的两倍。</t>
+          <t>1.a和ā 在</t>
         </is>
       </c>
     </row>
@@ -6540,18 +6812,26 @@
       <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr">
         <is>
-          <t>2.元音y代表着希腊语中upsilon(Y)，它读作法语的u(介于英语i和u之间)，发音可长可短，作长元音时的发音时间是作短元音时的两倍。</t>
+          <t>音质（quality ）上几乎一致</t>
         </is>
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="inlineStr"/>
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr"/>
-      <c r="C405" t="inlineStr"/>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D405" t="inlineStr"/>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Diphthongs</t>
+          <t>，只在</t>
         </is>
       </c>
     </row>
@@ -6566,33 +6846,37 @@
       <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr">
         <is>
-          <t>双元音</t>
+          <t>音量（quantity）上有所区别，</t>
         </is>
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="inlineStr"/>
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr"/>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr"/>
       <c r="E407" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A diphthong is a single vocalic sound made from pronouncing two vowels as one.(The word diphthong in Greek means "double sound.")</t>
+          <t>发音时一定要注意区别。</t>
         </is>
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A408" t="inlineStr"/>
       <c r="B408" t="inlineStr"/>
-      <c r="C408" t="inlineStr"/>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
-          <t>双元音是由两个元音合二为一的单一元音。(diphthong 在希腊语中的意思是“双重发音”。)</t>
+          <t>.All other pairs of vowels(e and e,etc.)differ both in quality and in quantity and are easier for the English speaker to differentiate.</t>
         </is>
       </c>
     </row>
@@ -6607,18 +6891,22 @@
       <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr">
         <is>
-          <t>双元音是两个元音在发音上合并，得到的一个元音。(diphthong 在希腊语中的意思是“双音”。)</t>
+          <t>所有其他元音对(e和ē等)</t>
         </is>
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr"/>
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr"/>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr">
         <is>
-          <t>There are six diphthongs in Latin, and they are pronounced as follows</t>
+          <t>在音质和音量</t>
         </is>
       </c>
     </row>
@@ -6633,35 +6921,31 @@
       <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr">
         <is>
-          <t>拉丁语中有六个双元音，它们的发音如下</t>
+          <t>上都不同，这对英语使用者（the English speaker）来说更容易区分。</t>
         </is>
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr"/>
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr"/>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr">
         <is>
-          <t>ae as the i of high</t>
+          <t>其他的元音对(e和ē等)在音质与音量上均不同，说英语的人更易区分它们。</t>
         </is>
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A413" t="inlineStr"/>
       <c r="B413" t="inlineStr"/>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr"/>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>ae读作high的i</t>
-        </is>
-      </c>
+      <c r="E413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr"/>
@@ -6670,7 +6954,7 @@
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr">
         <is>
-          <t xml:space="preserve"> oe as the oy of boy </t>
+          <t>2.y is a vowel representing the Greek upsilon(Y).This vowel is pronounced as a French u (a sound in between the English i and u).It may be long or short;the long vowel is pronounced twice as long as the short.</t>
         </is>
       </c>
     </row>
@@ -6685,18 +6969,26 @@
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr">
         <is>
-          <t>oe读作boy的oy</t>
+          <t>2.y是一个表示希腊语中的upsilon(Y)的元音。它发成法语的u(介于英语i和u之间)，</t>
         </is>
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr"/>
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr"/>
-      <c r="C416" t="inlineStr"/>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr">
         <is>
-          <t>ei as the ay of day</t>
+          <t>可长可短，而</t>
         </is>
       </c>
     </row>
@@ -6711,25 +7003,29 @@
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
-          <t>ei 读作day的ay</t>
+          <t>长元音的发音是短元音的两倍。</t>
         </is>
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr"/>
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr"/>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ui as the wi of twin </t>
+          <t>2.元音y代表着希腊语中upsilon(Y)，它读作法语的u(介于英语i和u之间)，发音可长可短，作长元音时的发音时间是作短元音时的两倍。</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -6737,7 +7033,7 @@
       <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ui 读作twin的wi </t>
+          <t>Diphthongs</t>
         </is>
       </c>
     </row>
@@ -6746,11 +7042,7 @@
       <c r="B420" t="inlineStr"/>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr"/>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t xml:space="preserve">au as the ow of how </t>
-        </is>
-      </c>
+      <c r="E420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -6763,18 +7055,22 @@
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr">
         <is>
-          <t>au读作how 的ow</t>
+          <t>双元音</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr"/>
       <c r="B422" t="inlineStr"/>
-      <c r="C422" t="inlineStr"/>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D422" t="inlineStr"/>
       <c r="E422" t="inlineStr">
         <is>
-          <t xml:space="preserve">eu as a combination of e+u </t>
+          <t xml:space="preserve"> A diphthong is a single vocalic sound made from pronouncing two vowels as one.(The word diphthong in Greek means "double sound.")</t>
         </is>
       </c>
     </row>
@@ -6789,7 +7085,7 @@
       <c r="D423" t="inlineStr"/>
       <c r="E423" t="inlineStr">
         <is>
-          <t>eu由e+u组合发音</t>
+          <t>双元音是由两个元音合二为一的单一元音。(diphthong 在希腊语中的意思是“双重发音”。)</t>
         </is>
       </c>
     </row>
@@ -6804,7 +7100,7 @@
       <c r="D424" t="inlineStr"/>
       <c r="E424" t="inlineStr">
         <is>
-          <t>eu的发音则是e和u的结合</t>
+          <t>双元音是两个元音在发音上合并，得到的一个元音。(diphthong 在希腊语中的意思是“双音”。)</t>
         </is>
       </c>
     </row>
@@ -6819,7 +7115,7 @@
       <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
-          <t>There is no English sound corresponding to the Latin diphthong eu.</t>
+          <t>There are six diphthongs in Latin, and they are pronounced as follows</t>
         </is>
       </c>
     </row>
@@ -6834,7 +7130,7 @@
       <c r="D426" t="inlineStr"/>
       <c r="E426" t="inlineStr">
         <is>
-          <t>英语中没有与拉丁双元音eu相对应的音。</t>
+          <t>拉丁语中有六个双元音，它们的发音如下</t>
         </is>
       </c>
     </row>
@@ -6845,7 +7141,7 @@
       <c r="D427" t="inlineStr"/>
       <c r="E427" t="inlineStr">
         <is>
-          <t>As its spelling indicates,it is a combination of the short vowels e and u pronounced as one sound</t>
+          <t>ae as the i of high</t>
         </is>
       </c>
     </row>
@@ -6860,18 +7156,22 @@
       <c r="D428" t="inlineStr"/>
       <c r="E428" t="inlineStr">
         <is>
-          <t>如其拼写所示，它由短元音e和u组合发为一个音</t>
+          <t>ae读作high的i</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr"/>
       <c r="B429" t="inlineStr"/>
-      <c r="C429" t="inlineStr"/>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D429" t="inlineStr"/>
       <c r="E429" t="inlineStr">
         <is>
-          <t>.If Elmer Fudd pronounced "very"(vewy),the ew would closely resemble the Latin sound of eu.</t>
+          <t xml:space="preserve"> oe as the oy of boy </t>
         </is>
       </c>
     </row>
@@ -6886,55 +7186,55 @@
       <c r="D430" t="inlineStr"/>
       <c r="E430" t="inlineStr">
         <is>
-          <t>若爱发先生（译注：系动画人物）将“very”发作“vewy”，那么“ew”的发音将与拉丁语中“eu”的发音非常相似。</t>
+          <t>oe读作boy的oy</t>
         </is>
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A431" t="inlineStr"/>
       <c r="B431" t="inlineStr"/>
       <c r="C431" t="inlineStr"/>
       <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
-          <t>爱发先生（译注：系动画人物）读“very”（“vewy”）时“ew”的发音与之非常相似。</t>
+          <t>ei as the ay of day</t>
         </is>
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="inlineStr"/>
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B432" t="inlineStr"/>
-      <c r="C432" t="inlineStr"/>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D432" t="inlineStr"/>
       <c r="E432" t="inlineStr">
         <is>
-          <t>5.All long vowels in this book are marked by macrons.Vowels not so marked are short.</t>
+          <t>ei 读作day的ay</t>
         </is>
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A433" t="inlineStr"/>
       <c r="B433" t="inlineStr"/>
       <c r="C433" t="inlineStr"/>
       <c r="D433" t="inlineStr"/>
       <c r="E433" t="inlineStr">
         <is>
-          <t>5.此书中所有长元音都将用长音符标记。若无则为短元音。</t>
+          <t xml:space="preserve"> ui as the wi of twin </t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -6942,7 +7242,7 @@
       <c r="D434" t="inlineStr"/>
       <c r="E434" t="inlineStr">
         <is>
-          <t>序号39，页数7（拆分：？，？）（机翻：？，？）（人翻：？，？）（第一次润色（按句）：？，？）（第一次校对：？，？）（第二次润色（按意群）：？，？）（第二次校对：？，？）（终润（按段落）：？，？）（终校：？，？）（附加评论/修改建议：？，？）（排版/美化：？，？）（美化后期再做）</t>
+          <t xml:space="preserve"> ui 读作twin的wi </t>
         </is>
       </c>
     </row>
@@ -6951,13 +7251,13 @@
       <c r="B435" t="inlineStr"/>
       <c r="C435" t="inlineStr">
         <is>
-          <t>【译者：Lanx】</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Stress</t>
+          <t xml:space="preserve">au as the ow of how </t>
         </is>
       </c>
     </row>
@@ -6972,26 +7272,18 @@
       <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
-          <t>重音</t>
+          <t>au读作how 的ow</t>
         </is>
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>【正文原文】</t>
-        </is>
-      </c>
+      <c r="A437" t="inlineStr"/>
       <c r="B437" t="inlineStr"/>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C437" t="inlineStr"/>
       <c r="D437" t="inlineStr"/>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Latin has a stress accent.This means that one syllable in a word is slightly stressed or emphasized when the word is pronounced.</t>
+          <t xml:space="preserve">eu as a combination of e+u </t>
         </is>
       </c>
     </row>
@@ -7002,11 +7294,15 @@
         </is>
       </c>
       <c r="B438" t="inlineStr"/>
-      <c r="C438" t="inlineStr"/>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D438" t="inlineStr"/>
       <c r="E438" t="inlineStr">
         <is>
-          <t>拉丁语重音意味着单词发音时要稍微重读或强调其中一个音节。</t>
+          <t>eu由e+u组合发音</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7317,7 @@
       <c r="D439" t="inlineStr"/>
       <c r="E439" t="inlineStr">
         <is>
-          <t>拉丁语有着一套重音体系，也就是说，在每个单词发音时需重读其中的一个音节。</t>
+          <t>eu的发音则是e和u的结合</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7332,7 @@
       <c r="D440" t="inlineStr"/>
       <c r="E440" t="inlineStr">
         <is>
-          <t>To determine which syllable is to be stressed,one must first divide a Latin word into syllables.</t>
+          <t>There is no English sound corresponding to the Latin diphthong eu.</t>
         </is>
       </c>
     </row>
@@ -7049,20 +7345,20 @@
       <c r="B441" t="inlineStr"/>
       <c r="C441" t="inlineStr">
         <is>
-          <t>【译者：Lanx】</t>
+          <t>【原文序号：3】</t>
         </is>
       </c>
       <c r="D441" t="inlineStr"/>
       <c r="E441" t="inlineStr">
         <is>
-          <t>要确定哪个音节应重读，须先将拉丁语单词进行音节划分。</t>
+          <t>英语中没有与拉丁双元音eu相对应的音。</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B442" t="inlineStr"/>
@@ -7070,59 +7366,47 @@
       <c r="D442" t="inlineStr"/>
       <c r="E442" t="inlineStr">
         <is>
-          <t>要确定重读哪个音节，须先对拉丁单词进行音节划分</t>
+          <t>As its spelling indicates,it is a combination of the short vowels e and u pronounced as one sound</t>
         </is>
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="inlineStr"/>
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr"/>
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr"/>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Syllabification</t>
+          <t>如其拼写所示，它由短元音e和u组合发为一个音</t>
         </is>
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A444" t="inlineStr"/>
       <c r="B444" t="inlineStr"/>
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr"/>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>音节划分</t>
-        </is>
-      </c>
+      <c r="E444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr"/>
       <c r="B445" t="inlineStr"/>
       <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr"/>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> A syllable is a sound or succession of sounds uttered with a single breath-impulse.</t>
-        </is>
-      </c>
+      <c r="E445" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A446" t="inlineStr"/>
       <c r="B446" t="inlineStr"/>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr"/>
       <c r="E446" t="inlineStr">
         <is>
-          <t>音节是单次</t>
+          <t>.If Elmer Fudd pronounced "very"(vewy),the ew would closely resemble the Latin sound of eu.</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7421,7 @@
       <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
-          <t>呼吸冲动</t>
+          <t>若爱发先生（译注：系动画人物）将“very”发作“vewy”，那么“ew”的发音将与拉丁语中“eu”的发音非常相似。</t>
         </is>
       </c>
     </row>
@@ -7152,22 +7436,18 @@
       <c r="D448" t="inlineStr"/>
       <c r="E448" t="inlineStr">
         <is>
-          <t>发出的声音或一连串的声音。</t>
+          <t>爱发先生（译注：系动画人物）读“very”（“vewy”）时“ew”的发音与之非常相似。</t>
         </is>
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A449" t="inlineStr"/>
       <c r="B449" t="inlineStr"/>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
-          <t>音节是在单次</t>
+          <t>5.All long vowels in this book are marked by macrons.Vowels not so marked are short.</t>
         </is>
       </c>
     </row>
@@ -7182,33 +7462,41 @@
       <c r="D450" t="inlineStr"/>
       <c r="E450" t="inlineStr">
         <is>
-          <t>呼出气流</t>
+          <t>5.此书中所有长元音都将用长音符标记。若无则为短元音。</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【分工】</t>
         </is>
       </c>
       <c r="B451" t="inlineStr"/>
-      <c r="C451" t="inlineStr"/>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D451" t="inlineStr"/>
       <c r="E451" t="inlineStr">
         <is>
-          <t>内发出的一声或一连串声音</t>
+          <t>序号39，页数7（拆分：？，？）（机翻：？，？）（人翻：？，？）（第一次润色（按句）：？，？）（第一次校对：？，？）（第二次润色（按意群）：？，？）（第二次校对：？，？）（终润（按段落）：？，？）（终校：？，？）（附加评论/修改建议：？，？）（排版/美化：？，？）（美化后期再做）</t>
         </is>
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="inlineStr"/>
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr"/>
       <c r="C452" t="inlineStr"/>
       <c r="D452" t="inlineStr"/>
       <c r="E452" t="inlineStr">
         <is>
-          <t>A LATIN WORD HAS AS MANY SYLLABLES AS IT HAS VOWELS OR DIPHTHONGS.THERE ARE NO SILENT VOWELS OR CONSONANTS IN LATIN.</t>
+          <t>Stress</t>
         </is>
       </c>
     </row>
@@ -7227,14 +7515,14 @@
       <c r="D453" t="inlineStr"/>
       <c r="E453" t="inlineStr">
         <is>
-          <t>谨记，拉丁语单词音节数量和它的元音或双元音数量一样多。拉丁语中没有不发音的元音或辅音。</t>
+          <t>重音</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B454" t="inlineStr"/>
@@ -7242,18 +7530,22 @@
       <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
-          <t>谨记，拉丁语单词的音节和元音或双元音在（数量上）一样多。拉丁语中没有不发音的元音或辅音。</t>
+          <t>Latin has a stress accent.This means that one syllable in a word is slightly stressed or emphasized when the word is pronounced.</t>
         </is>
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr"/>
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B455" t="inlineStr"/>
       <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr"/>
       <c r="E455" t="inlineStr">
         <is>
-          <t xml:space="preserve">When a word is divided into syllables, </t>
+          <t>拉丁语重音意味着单词发音时要稍微重读或强调其中一个音节。</t>
         </is>
       </c>
     </row>
@@ -7268,33 +7560,41 @@
       <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
-          <t>当单词划分为音节时，遵循以下规则，</t>
+          <t>拉丁语有着一套重音体系，也就是说，在每个单词发音时需重读其中的一个音节。</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B457" t="inlineStr"/>
-      <c r="C457" t="inlineStr"/>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr">
         <is>
-          <t>遵循下列规则以划分音节：</t>
+          <t>To determine which syllable is to be stressed,one must first divide a Latin word into syllables.</t>
         </is>
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="inlineStr"/>
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr"/>
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr"/>
       <c r="E458" t="inlineStr">
         <is>
-          <t>1.a single consonant goes with the following vowel:</t>
+          <t>要确定哪个音节应重读，须先将拉丁语单词进行音节划分。</t>
         </is>
       </c>
     </row>
@@ -7305,15 +7605,11 @@
         </is>
       </c>
       <c r="B459" t="inlineStr"/>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr">
         <is>
-          <t>1.单辅音（single consonant）后跟元音:</t>
+          <t>要确定重读哪个音节，须先对拉丁单词进行音节划分</t>
         </is>
       </c>
     </row>
@@ -7328,18 +7624,22 @@
       <c r="D460" t="inlineStr"/>
       <c r="E460" t="inlineStr">
         <is>
-          <t xml:space="preserve"> anima  a/ni/ma </t>
+          <t>Syllabification</t>
         </is>
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="inlineStr"/>
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr"/>
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr">
         <is>
-          <t xml:space="preserve"> aurum au/rum</t>
+          <t>音节划分</t>
         </is>
       </c>
     </row>
@@ -7350,25 +7650,29 @@
       <c r="D462" t="inlineStr"/>
       <c r="E462" t="inlineStr">
         <is>
-          <t xml:space="preserve"> gladius   gla/di/us</t>
+          <t xml:space="preserve"> A syllable is a sound or succession of sounds uttered with a single breath-impulse.</t>
         </is>
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="inlineStr"/>
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B463" t="inlineStr"/>
       <c r="C463" t="inlineStr"/>
       <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr">
         <is>
-          <t xml:space="preserve">vitaque  vi/ta/que </t>
+          <t>音节是单次</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -7376,14 +7680,14 @@
       <c r="D464" t="inlineStr"/>
       <c r="E464" t="inlineStr">
         <is>
-          <t>8.2 改到这里</t>
+          <t>呼吸冲动</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>【批注】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -7391,18 +7695,22 @@
       <c r="D465" t="inlineStr"/>
       <c r="E465" t="inlineStr">
         <is>
-          <t>8.3 同上</t>
+          <t>发出的声音或一连串的声音。</t>
         </is>
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="inlineStr"/>
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B466" t="inlineStr"/>
       <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr"/>
       <c r="E466" t="inlineStr">
         <is>
-          <t xml:space="preserve"> qu always counts as a single consonant.su and gu sometimes count as single consonants.</t>
+          <t>音节是在单次</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7725,7 @@
       <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr">
         <is>
-          <t>qu总是算作单辅音。su和gu有时视为单辅音。</t>
+          <t>呼出气流</t>
         </is>
       </c>
     </row>
@@ -7432,18 +7740,26 @@
       <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr">
         <is>
-          <t>qu是个单辅音，而su和gu有时视为单辅音</t>
+          <t>内发出的一声或一连串声音</t>
         </is>
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="inlineStr"/>
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B469" t="inlineStr"/>
-      <c r="C469" t="inlineStr"/>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D469" t="inlineStr"/>
       <c r="E469" t="inlineStr">
         <is>
-          <t>2.if there are two or more consonants in a row,the last consonant goes with the following syllable:</t>
+          <t>A LATIN WORD HAS AS MANY SYLLABLES AS IT HAS VOWELS OR DIPHTHONGS.THERE ARE NO SILENT VOWELS OR CONSONANTS IN LATIN.</t>
         </is>
       </c>
     </row>
@@ -7458,7 +7774,7 @@
       <c r="D470" t="inlineStr"/>
       <c r="E470" t="inlineStr">
         <is>
-          <t>2.若连续有两个或以上的辅音，则后面的辅音计入下一个音节:</t>
+          <t>谨记，拉丁语单词音节数量和它的元音或双元音数量一样多。拉丁语中没有不发音的元音或辅音。</t>
         </is>
       </c>
     </row>
@@ -7469,108 +7785,108 @@
         </is>
       </c>
       <c r="B471" t="inlineStr"/>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr"/>
       <c r="E471" t="inlineStr">
         <is>
-          <t>2.若有两个或以上连在一起的辅音，则最后的辅音计入下一个音节:</t>
+          <t>谨记，拉丁语单词的音节和元音或双元音在（数量上）一样多。拉丁语中没有不发音的元音或辅音。</t>
         </is>
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="inlineStr"/>
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B472" t="inlineStr"/>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr"/>
       <c r="E472" t="inlineStr">
         <is>
-          <t xml:space="preserve"> imperium im/pe/ri/um </t>
+          <t xml:space="preserve">When a word is divided into syllables, </t>
         </is>
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="inlineStr"/>
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B473" t="inlineStr"/>
       <c r="C473" t="inlineStr"/>
       <c r="D473" t="inlineStr"/>
       <c r="E473" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanctus sanc/tus </t>
+          <t>当单词划分为音节时，遵循以下规则，</t>
         </is>
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="inlineStr"/>
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B474" t="inlineStr"/>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr"/>
       <c r="E474" t="inlineStr">
         <is>
-          <t>virumque vi/rum/que</t>
+          <t>遵循下列规则以划分音节：</t>
         </is>
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>【正文原文】</t>
-        </is>
-      </c>
+      <c r="A475" t="inlineStr"/>
       <c r="B475" t="inlineStr"/>
-      <c r="C475" t="inlineStr"/>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
-          <t xml:space="preserve"> puella pu/el/la</t>
+          <t>1.a single consonant goes with the following vowel:</t>
         </is>
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="inlineStr"/>
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B476" t="inlineStr"/>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 3.if,however,the combination of two consonants is a mute (c.k.t.p,ch,th.ph,g.d.b)or the fricative f followed by a liquid(1.r).the two consonants are kept together. 6</t>
+          <t>1.单辅音（single consonant）后跟元音:</t>
         </is>
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A477" t="inlineStr"/>
       <c r="B477" t="inlineStr"/>
-      <c r="C477" t="inlineStr">
-        <is>
-          <t>【译者：Lanx】</t>
-        </is>
-      </c>
+      <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr"/>
       <c r="E477" t="inlineStr">
         <is>
-          <t>3.然而，若两个辅音组合成一个塞音（mute）(c.k.t.p,ch,th.ph,g.d.b)或擦音（fricative）f后面跟着一个流音（liquid）(l.r)。两个辅音视为一个辅音组。6</t>
+          <t xml:space="preserve"> anima  a/ni/ma </t>
         </is>
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A478" t="inlineStr"/>
       <c r="B478" t="inlineStr"/>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr"/>
       <c r="E478" t="inlineStr">
         <is>
-          <t>3.但当两个辅音构成一个塞音（mute）(c.k.t.p,ch,th.ph,g.d.b)或擦音（fricative）f后跟着一个流音（liquid）(l.r)时，这样的两个辅音划入同一音节。</t>
+          <t xml:space="preserve"> aurum au/rum</t>
         </is>
       </c>
     </row>
@@ -7581,7 +7897,7 @@
       <c r="D479" t="inlineStr"/>
       <c r="E479" t="inlineStr">
         <is>
-          <t>patria pa/tri/a</t>
+          <t xml:space="preserve"> gladius   gla/di/us</t>
         </is>
       </c>
     </row>
@@ -7590,61 +7906,57 @@
       <c r="B480" t="inlineStr"/>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr"/>
-      <c r="E480" t="inlineStr">
-        <is>
-          <t xml:space="preserve">agricola a/gri/co/la </t>
-        </is>
-      </c>
+      <c r="E480" t="inlineStr"/>
     </row>
     <row r="481">
-      <c r="A481" t="inlineStr"/>
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B481" t="inlineStr"/>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr"/>
       <c r="E481" t="inlineStr">
         <is>
-          <t xml:space="preserve">ablatus  a/bla/tus </t>
+          <t>并指出散文与诗歌的区别，但在大多数情况下，书中的古典拉丁语规则仅适用于这一特定时期的文学作品</t>
         </is>
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="inlineStr"/>
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B482" t="inlineStr"/>
       <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr"/>
       <c r="E482" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accentuation </t>
+          <t>8.2 改到这里</t>
         </is>
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A483" t="inlineStr"/>
       <c r="B483" t="inlineStr"/>
       <c r="C483" t="inlineStr"/>
       <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr">
         <is>
-          <t>重读</t>
+          <t xml:space="preserve">vitaque  vi/ta/que </t>
         </is>
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>【正文原文】</t>
-        </is>
-      </c>
+      <c r="A484" t="inlineStr"/>
       <c r="B484" t="inlineStr"/>
       <c r="C484" t="inlineStr"/>
       <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr">
         <is>
-          <t>The last syllable in a Latin word is called the ultima(&lt;syllaba ultima,"last syllable").</t>
+          <t xml:space="preserve"> qu always counts as a single consonant.su and gu sometimes count as single consonants.</t>
         </is>
       </c>
     </row>
@@ -7659,14 +7971,14 @@
       <c r="D485" t="inlineStr"/>
       <c r="E485" t="inlineStr">
         <is>
-          <t>拉丁语单词的最后一个音节称为倒数第一音节（ultima）(&lt; syllable ultima，“最后的音节”)。</t>
+          <t>qu总是算作单辅音。su和gu有时视为单辅音。</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -7674,37 +7986,37 @@
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr">
         <is>
-          <t>The second syllable from the end is called the penult(syllaba paenultima."almost last syllable").</t>
+          <t>qu是个单辅音，而su和gu有时视为单辅音</t>
         </is>
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A487" t="inlineStr"/>
       <c r="B487" t="inlineStr"/>
       <c r="C487" t="inlineStr"/>
       <c r="D487" t="inlineStr"/>
       <c r="E487" t="inlineStr">
         <is>
-          <t>从最后倒数的第二个音节被称为倒数第二音节（penult）。(syllaba paenultima.“几乎最后的音节”)。</t>
+          <t>2.if there are two or more consonants in a row,the last consonant goes with the following syllable:</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B488" t="inlineStr"/>
-      <c r="C488" t="inlineStr"/>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr">
         <is>
-          <t>The third syllable from the end is called the antepenult(&lt;syllaba an-tepaenultima."before-the-almost-last syllable").</t>
+          <t>2.若连续有两个或以上的辅音，则后面的辅音计入下一个音节:</t>
         </is>
       </c>
     </row>
@@ -7719,22 +8031,18 @@
       <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr">
         <is>
-          <t>从末尾开始的第三个音节被称为倒数第三音节（antepenult）(&lt; syllable antepaenultima)。“几乎最后音节的前一个音节”)。</t>
+          <t>2.若有两个或以上连在一起的辅音，则最后的辅音计入下一个音节:</t>
         </is>
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A490" t="inlineStr"/>
       <c r="B490" t="inlineStr"/>
       <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>上面三句先跳过吧</t>
+          <t xml:space="preserve"> imperium im/pe/ri/um </t>
         </is>
       </c>
     </row>
@@ -7745,89 +8053,65 @@
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
-          <t>6. A consonant that requires a stoppage of breath when pronounced is called a mute.</t>
+          <t xml:space="preserve">sanctus sanc/tus </t>
         </is>
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A492" t="inlineStr"/>
       <c r="B492" t="inlineStr"/>
       <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr"/>
       <c r="E492" t="inlineStr">
         <is>
-          <t>6. 发音时需要暂停呼吸的辅音称为塞音。（mute）</t>
+          <t>virumque vi/rum/que</t>
         </is>
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A493" t="inlineStr"/>
       <c r="B493" t="inlineStr"/>
       <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr"/>
       <c r="E493" t="inlineStr">
         <is>
-          <t>6. 发音时需要阻塞呼吸的辅音称为塞音。（mute）</t>
+          <t xml:space="preserve"> puella pu/el/la</t>
         </is>
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>【正文原文】</t>
-        </is>
-      </c>
+      <c r="A494" t="inlineStr"/>
       <c r="B494" t="inlineStr"/>
-      <c r="C494" t="inlineStr"/>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D494" t="inlineStr"/>
       <c r="E494" t="inlineStr">
         <is>
-          <t xml:space="preserve"> When a g is pronounced, for example, the throat is contracted and breath is stopped.</t>
+          <t xml:space="preserve"> 3.if,however,the combination of two consonants is a mute (c.k.t.p,ch,th.ph,g.d.b)or the fricative f followed by a liquid(1.r).the two consonants are kept together. 6</t>
         </is>
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A495" t="inlineStr"/>
       <c r="B495" t="inlineStr"/>
       <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr"/>
-      <c r="E495" t="inlineStr">
-        <is>
-          <t>例如，发g音时，喉咙收缩，呼吸停止。</t>
-        </is>
-      </c>
+      <c r="E495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A496" t="inlineStr"/>
       <c r="B496" t="inlineStr"/>
       <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr"/>
-      <c r="E496" t="inlineStr">
-        <is>
-          <t>例如，g发音时，喉咙收紧，呼吸阻塞。</t>
-        </is>
-      </c>
+      <c r="E496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -7835,7 +8119,7 @@
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Similarly, when a p is pro nounced, the lips are closed and breath is again stopped.</t>
+          <t>3.然而，若两个辅音组合成一个塞音（mute）(c.k.t.p,ch,th.ph,g.d.b)或擦音（fricative）f后面跟着一个流音（liquid）(l.r)。两个辅音视为一个辅音组。6</t>
         </is>
       </c>
     </row>
@@ -7850,22 +8134,18 @@
       <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
-          <t>同样，发p音时，嘴唇紧闭，呼吸再次停止。</t>
+          <t>3.但当两个辅音构成一个塞音（mute）(c.k.t.p,ch,th.ph,g.d.b)或擦音（fricative）f后跟着一个流音（liquid）(l.r)时，这样的两个辅音划入同一音节。</t>
         </is>
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A499" t="inlineStr"/>
       <c r="B499" t="inlineStr"/>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>同样，p发音时，嘴唇紧闭，呼吸亦阻塞。</t>
+          <t>patria pa/tri/a</t>
         </is>
       </c>
     </row>
@@ -7876,55 +8156,59 @@
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t xml:space="preserve"> A fricative is a consonant produced by forcing breath through a constricted passage. </t>
+          <t xml:space="preserve">agricola a/gri/co/la </t>
         </is>
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A501" t="inlineStr"/>
       <c r="B501" t="inlineStr"/>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr"/>
       <c r="E501" t="inlineStr">
         <is>
-          <t>擦音是通过压缩通道强制呼吸而产生的辅音。</t>
+          <t xml:space="preserve">ablatus  a/bla/tus </t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B502" t="inlineStr"/>
-      <c r="C502" t="inlineStr"/>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>擦音由压迫气流通过收紧的呼吸道产生，是辅音。</t>
+          <t xml:space="preserve">Accentuation </t>
         </is>
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="inlineStr"/>
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B503" t="inlineStr"/>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
-          <t>l and r are called liquids because their sounds are capable of being prolonged as vowels.</t>
+          <t>重读</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B504" t="inlineStr"/>
@@ -7932,14 +8216,14 @@
       <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
-          <t>L和r称为流音，它们的发音可像元音般延长。</t>
+          <t>The last syllable in a Latin word is called the ultima(&lt;syllaba ultima,"last syllable").</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>【分工】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B505" t="inlineStr"/>
@@ -7947,18 +8231,22 @@
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>序号40，页数8（拆分：？，？）（机翻：？，？）（人翻：？，？）（第一次润色（按句）：？，？）（第一次校对：？，？）（第二次润色（按意群）：？，？）（第二次校对：？，？）（终润（按段落）：？，？）（终校：？，？）（附加评论/修改建议：？，？）（排版/美化：？，？）（美化后期再做）</t>
+          <t>拉丁语单词的最后一个音节称为倒数第一音节（ultima）(&lt; syllable ultima，“最后的音节”)。</t>
         </is>
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="inlineStr"/>
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B506" t="inlineStr"/>
       <c r="C506" t="inlineStr"/>
       <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
-          <t>ONLY THE PENULT OR THE ANTEPENULT OF A LATIN WORD MAY BE STRESSED.</t>
+          <t>The second syllable from the end is called the penult(syllaba paenultima."almost last syllable").</t>
         </is>
       </c>
     </row>
@@ -7969,11 +8257,15 @@
         </is>
       </c>
       <c r="B507" t="inlineStr"/>
-      <c r="C507" t="inlineStr"/>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr">
         <is>
-          <t>谨记，只有拉丁单词的倒数第二或第三音节可以重读。</t>
+          <t>从最后倒数的第二个音节被称为倒数第二音节（penult）。(syllaba paenultima.“几乎最后的音节”)。</t>
         </is>
       </c>
     </row>
@@ -7988,7 +8280,7 @@
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr">
         <is>
-          <t>If a word has only two syllables,the penult is stressed.The following words are stressed on the penult because they have two syllables only.</t>
+          <t>The third syllable from the end is called the antepenult(&lt;syllaba an-tepaenultima."before-the-almost-last syllable").</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8295,7 @@
       <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
-          <t>若单词只有两个音节，那么倒数第二音节重读。</t>
+          <t>从末尾开始的第三个音节被称为倒数第三音节（antepenult）(&lt; syllable antepaenultima)。“几乎最后音节的前一个音节”)。</t>
         </is>
       </c>
     </row>
@@ -8014,37 +8306,41 @@
         </is>
       </c>
       <c r="B510" t="inlineStr"/>
-      <c r="C510" t="inlineStr"/>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
-          <t>若单词只有两个音节，那么重读倒数第二音节。</t>
+          <t>上面三句先跳过吧</t>
         </is>
       </c>
     </row>
     <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A511" t="inlineStr"/>
       <c r="B511" t="inlineStr"/>
       <c r="C511" t="inlineStr"/>
       <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
-          <t>（后面一句是废话，删了）</t>
+          <t>6. A consonant that requires a stoppage of breath when pronounced is called a mute.</t>
         </is>
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="inlineStr"/>
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B512" t="inlineStr"/>
       <c r="C512" t="inlineStr"/>
       <c r="D512" t="inlineStr"/>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Practice pronouncing them out loud, stressing the penult.</t>
+          <t>6. 发音时需要暂停呼吸的辅音称为塞音。（mute）</t>
         </is>
       </c>
     </row>
@@ -8055,11 +8351,15 @@
         </is>
       </c>
       <c r="B513" t="inlineStr"/>
-      <c r="C513" t="inlineStr"/>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr">
         <is>
-          <t>请大声练习下列单词，重读倒数第二音节。</t>
+          <t>6. 发音时需要阻塞呼吸的辅音称为塞音。（mute）</t>
         </is>
       </c>
     </row>
@@ -8070,44 +8370,52 @@
       <c r="D514" t="inlineStr"/>
       <c r="E514" t="inlineStr">
         <is>
-          <t xml:space="preserve">tamen consul </t>
+          <t xml:space="preserve"> When a g is pronounced, for example, the throat is contracted and breath is stopped.</t>
         </is>
       </c>
     </row>
     <row r="515">
-      <c r="A515" t="inlineStr"/>
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B515" t="inlineStr"/>
       <c r="C515" t="inlineStr"/>
       <c r="D515" t="inlineStr"/>
       <c r="E515" t="inlineStr">
         <is>
-          <t>mutat  opus</t>
+          <t>例如，发g音时，喉咙收缩，呼吸停止。</t>
         </is>
       </c>
     </row>
     <row r="516">
-      <c r="A516" t="inlineStr"/>
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B516" t="inlineStr"/>
-      <c r="C516" t="inlineStr"/>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D516" t="inlineStr"/>
       <c r="E516" t="inlineStr">
         <is>
-          <t xml:space="preserve"> If a word has more than two syllables,its stress is determined according to a rule called the law of the penult:</t>
+          <t>例如，g发音时，喉咙收紧，呼吸阻塞。</t>
         </is>
       </c>
     </row>
     <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A517" t="inlineStr"/>
       <c r="B517" t="inlineStr"/>
       <c r="C517" t="inlineStr"/>
       <c r="D517" t="inlineStr"/>
       <c r="E517" t="inlineStr">
         <is>
-          <t>若单词有两个以上音节，则根据</t>
+          <t xml:space="preserve"> Similarly, when a p is pro nounced, the lips are closed and breath is again stopped.</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8430,7 @@
       <c r="D518" t="inlineStr"/>
       <c r="E518" t="inlineStr">
         <is>
-          <t>倒数定律规则（law of the penult）</t>
+          <t>同样，发p音时，嘴唇紧闭，呼吸再次停止。</t>
         </is>
       </c>
     </row>
@@ -8133,11 +8441,15 @@
         </is>
       </c>
       <c r="B519" t="inlineStr"/>
-      <c r="C519" t="inlineStr"/>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D519" t="inlineStr"/>
       <c r="E519" t="inlineStr">
         <is>
-          <t>确定重音:</t>
+          <t>同样，p发音时，嘴唇紧闭，呼吸亦阻塞。</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8460,7 @@
       <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr">
         <is>
-          <t xml:space="preserve"> IF THE PENULT IS LONG,IT IS STRESSED.IF THE PENULT IS SHORT,THE ANTE- PENULT IS STRESSED.</t>
+          <t xml:space="preserve"> A fricative is a consonant produced by forcing breath through a constricted passage. </t>
         </is>
       </c>
     </row>
@@ -8163,18 +8475,22 @@
       <c r="D521" t="inlineStr"/>
       <c r="E521" t="inlineStr">
         <is>
-          <t>谨记，若倒数第二音节是长音，则重读。若是短音，则重读倒数第三音节。</t>
+          <t>擦音是通过压缩通道强制呼吸而产生的辅音。</t>
         </is>
       </c>
     </row>
     <row r="522">
-      <c r="A522" t="inlineStr"/>
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B522" t="inlineStr"/>
       <c r="C522" t="inlineStr"/>
       <c r="D522" t="inlineStr"/>
       <c r="E522" t="inlineStr">
         <is>
-          <t xml:space="preserve">agricola a/gri/co/la </t>
+          <t>擦音由压迫气流通过收紧的呼吸道产生，是辅音。</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8501,7 @@
       <c r="D523" t="inlineStr"/>
       <c r="E523" t="inlineStr">
         <is>
-          <t>A syllable is long if it contains:</t>
+          <t>l and r are called liquids because their sounds are capable of being prolonged as vowels.</t>
         </is>
       </c>
     </row>
@@ -8196,29 +8512,37 @@
         </is>
       </c>
       <c r="B524" t="inlineStr"/>
-      <c r="C524" t="inlineStr"/>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D524" t="inlineStr"/>
       <c r="E524" t="inlineStr">
         <is>
-          <t>若音节包含以下内容，则为长音:</t>
+          <t>L和r称为流音，它们的发音可像元音般延长。</t>
         </is>
       </c>
     </row>
     <row r="525">
-      <c r="A525" t="inlineStr"/>
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>【分工】</t>
+        </is>
+      </c>
       <c r="B525" t="inlineStr"/>
       <c r="C525" t="inlineStr"/>
       <c r="D525" t="inlineStr"/>
       <c r="E525" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.a long vowel or diphthong (long by nature) </t>
+          <t>序号40，页数8（拆分：？，？）（机翻：？，？）（人翻：？，？）（第一次润色（按句）：？，？）（第一次校对：？，？）（第二次润色（按意群）：？，？）（第二次校对：？，？）（终润（按段落）：？，？）（终校：？，？）（附加评论/修改建议：？，？）（排版/美化：？，？）（美化后期再做）</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B526" t="inlineStr"/>
@@ -8226,25 +8550,33 @@
       <c r="D526" t="inlineStr"/>
       <c r="E526" t="inlineStr">
         <is>
-          <t xml:space="preserve">单长元音或双元音(自然长)(long by nature) </t>
+          <t>ONLY THE PENULT OR THE ANTEPENULT OF A LATIN WORD MAY BE STRESSED.</t>
         </is>
       </c>
     </row>
     <row r="527">
-      <c r="A527" t="inlineStr"/>
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B527" t="inlineStr"/>
-      <c r="C527" t="inlineStr"/>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.a short vowel followed by two or more consonants not necessarily in the same syllable (long by position) </t>
+          <t>谨记，只有拉丁单词的倒数第二或第三音节可以重读。</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B528" t="inlineStr"/>
@@ -8252,18 +8584,22 @@
       <c r="D528" t="inlineStr"/>
       <c r="E528" t="inlineStr">
         <is>
-          <t>短元音后跟两个或以上辅音，但不一定在同音节中(位置长) (long by position) 。</t>
+          <t>If a word has only two syllables,the penult is stressed.The following words are stressed on the penult because they have two syllables only.</t>
         </is>
       </c>
     </row>
     <row r="529">
-      <c r="A529" t="inlineStr"/>
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B529" t="inlineStr"/>
       <c r="C529" t="inlineStr"/>
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr">
         <is>
-          <t>The following words are stressed on the penult because their penults are long by nature</t>
+          <t>若单词只有两个音节，那么倒数第二音节重读。</t>
         </is>
       </c>
     </row>
@@ -8274,29 +8610,37 @@
         </is>
       </c>
       <c r="B530" t="inlineStr"/>
-      <c r="C530" t="inlineStr"/>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr">
         <is>
-          <t>以下单词重读倒数第二音节，因为它们的倒数第二音节是自然长。</t>
+          <t>若单词只有两个音节，那么重读倒数第二音节。</t>
         </is>
       </c>
     </row>
     <row r="531">
-      <c r="A531" t="inlineStr"/>
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B531" t="inlineStr"/>
       <c r="C531" t="inlineStr"/>
       <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr">
         <is>
-          <t>.Practice pronouncing them out loud,stressing the penult.</t>
+          <t>（后面一句是废话，删了）</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>【正文译文】</t>
+          <t>【正文原文】</t>
         </is>
       </c>
       <c r="B532" t="inlineStr"/>
@@ -8304,7 +8648,7 @@
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr">
         <is>
-          <t>请大声练习</t>
+          <t>Practice pronouncing them out loud, stressing the penult.</t>
         </is>
       </c>
     </row>
@@ -8319,18 +8663,22 @@
       <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr">
         <is>
-          <t>（后面一句是废话，删了）</t>
+          <t>请大声练习下列单词，重读倒数第二音节。</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr"/>
       <c r="B534" t="inlineStr"/>
-      <c r="C534" t="inlineStr"/>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D534" t="inlineStr"/>
       <c r="E534" t="inlineStr">
         <is>
-          <t xml:space="preserve">inimicus figura </t>
+          <t xml:space="preserve">tamen consul </t>
         </is>
       </c>
     </row>
@@ -8341,7 +8689,7 @@
       <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr">
         <is>
-          <t xml:space="preserve"> magnarum labores </t>
+          <t>mutat  opus</t>
         </is>
       </c>
     </row>
@@ -8352,74 +8700,70 @@
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr">
         <is>
-          <t xml:space="preserve">patiemur persaepe </t>
+          <t xml:space="preserve"> If a word has more than two syllables,its stress is determined according to a rule called the law of the penult:</t>
         </is>
       </c>
     </row>
     <row r="537">
-      <c r="A537" t="inlineStr"/>
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B537" t="inlineStr"/>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr">
         <is>
-          <t xml:space="preserve">poeta perpauca </t>
+          <t>若单词有两个以上音节，则根据</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>【正文原文】</t>
+          <t>【正文译文】</t>
         </is>
       </c>
       <c r="B538" t="inlineStr"/>
-      <c r="C538" t="inlineStr"/>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>【原文序号：3】</t>
+        </is>
+      </c>
       <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr">
         <is>
-          <t>The following words are stressed on the penult because their penults are long by position.Practice pronouncing them out loud,stressing the penult.</t>
+          <t>倒数定律规则（law of the penult）</t>
         </is>
       </c>
     </row>
     <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A539" t="inlineStr"/>
       <c r="B539" t="inlineStr"/>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr">
-        <is>
-          <t>以下单词重读倒数第二音节，因为它们的倒数第二音节是位置长。请大声练习</t>
-        </is>
-      </c>
+      <c r="E539" t="inlineStr"/>
     </row>
     <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>【正文译文】</t>
-        </is>
-      </c>
+      <c r="A540" t="inlineStr"/>
       <c r="B540" t="inlineStr"/>
       <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr">
-        <is>
-          <t>（后面一句是废话，删了）</t>
-        </is>
-      </c>
+      <c r="E540" t="inlineStr"/>
     </row>
     <row r="541">
-      <c r="A541" t="inlineStr"/>
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B541" t="inlineStr"/>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
-          <t xml:space="preserve">ocellis contactum </t>
+          <t>确定重音:</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8774,7 @@
       <c r="D542" t="inlineStr"/>
       <c r="E542" t="inlineStr">
         <is>
-          <t>magister expressit</t>
+          <t xml:space="preserve"> IF THE PENULT IS LONG,IT IS STRESSED.IF THE PENULT IS SHORT,THE ANTE- PENULT IS STRESSED.</t>
         </is>
       </c>
     </row>
@@ -8441,29 +8785,37 @@
       <c r="D543" t="inlineStr"/>
       <c r="E543" t="inlineStr">
         <is>
-          <t xml:space="preserve"> intellegenda   adversos </t>
+          <t>patria pa/tri/a</t>
         </is>
       </c>
     </row>
     <row r="544">
-      <c r="A544" t="inlineStr"/>
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B544" t="inlineStr"/>
       <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr"/>
       <c r="E544" t="inlineStr">
         <is>
-          <t xml:space="preserve">conferri deportant </t>
+          <t>谨记，若倒数第二音节是长音，则重读。若是短音，则重读倒数第三音节。</t>
         </is>
       </c>
     </row>
     <row r="545">
-      <c r="A545" t="inlineStr"/>
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B545" t="inlineStr"/>
       <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr"/>
       <c r="E545" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1.In words of more than two syllables,the number of syllables is not important for determining the syllable to be stressed.Only the length of the penult determines stress.</t>
+          <t>A syllable is long if it contains:</t>
         </is>
       </c>
     </row>
@@ -8474,11 +8826,15 @@
         </is>
       </c>
       <c r="B546" t="inlineStr"/>
-      <c r="C546" t="inlineStr"/>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
       <c r="D546" t="inlineStr"/>
       <c r="E546" t="inlineStr">
         <is>
-          <t>1.两个音节以上的单词中，音节数量并不影响重读音节，只有倒数第二音节的长度才能影响。</t>
+          <t>若音节包含以下内容，则为长音:</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8845,7 @@
       <c r="D547" t="inlineStr"/>
       <c r="E547" t="inlineStr">
         <is>
-          <t>2.The lengths of the syllables other than the penult are not important for determining stress.</t>
+          <t xml:space="preserve"> 1.a long vowel or diphthong (long by nature) </t>
         </is>
       </c>
     </row>
@@ -8504,22 +8860,18 @@
       <c r="D548" t="inlineStr"/>
       <c r="E548" t="inlineStr">
         <is>
-          <t>2.倒数第二音节以外的音节长度不影响重读音节。</t>
+          <t xml:space="preserve">单长元音或双元音(自然长)(long by nature) </t>
         </is>
       </c>
     </row>
     <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>【正文原文】</t>
-        </is>
-      </c>
+      <c r="A549" t="inlineStr"/>
       <c r="B549" t="inlineStr"/>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr"/>
       <c r="E549" t="inlineStr">
         <is>
-          <t>The following words are stressed on the antepenult because their penults are short.Practice pronouncing them out loud,stressing the antepenult.</t>
+          <t xml:space="preserve">2.a short vowel followed by two or more consonants not necessarily in the same syllable (long by position) </t>
         </is>
       </c>
     </row>
@@ -8534,29 +8886,320 @@
       <c r="D550" t="inlineStr"/>
       <c r="E550" t="inlineStr">
         <is>
-          <t>以下单词重读倒数第三音节，因为它们的倒数第三音节是短音节，请大声练习。（后面一句是废话，删了）</t>
+          <t>短元音后跟两个或以上辅音，但不一定在同音节中(位置长) (long by position) 。</t>
         </is>
       </c>
     </row>
     <row r="551">
-      <c r="A551" t="inlineStr"/>
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
       <c r="B551" t="inlineStr"/>
       <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr"/>
       <c r="E551" t="inlineStr">
         <is>
-          <t xml:space="preserve">scientia tempora </t>
+          <t>The following words are stressed on the penult because their penults are long by nature</t>
         </is>
       </c>
     </row>
     <row r="552">
-      <c r="A552" t="inlineStr"/>
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
       <c r="B552" t="inlineStr"/>
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr"/>
       <c r="E552" t="inlineStr">
         <is>
-          <t xml:space="preserve">aequora mediocriter </t>
+          <t>以下单词重读倒数第二音节，因为它们的倒数第二音节是自然长。</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr"/>
+      <c r="B553" t="inlineStr"/>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr"/>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>.Practice pronouncing them out loud,stressing the penult.</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr"/>
+      <c r="C554" t="inlineStr"/>
+      <c r="D554" t="inlineStr"/>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>请大声练习</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr"/>
+      <c r="C555" t="inlineStr"/>
+      <c r="D555" t="inlineStr"/>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>（后面一句是废话，删了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr"/>
+      <c r="B556" t="inlineStr"/>
+      <c r="C556" t="inlineStr"/>
+      <c r="D556" t="inlineStr"/>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inimicus figura </t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr"/>
+      <c r="B557" t="inlineStr"/>
+      <c r="C557" t="inlineStr"/>
+      <c r="D557" t="inlineStr"/>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> magnarum labores </t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr"/>
+      <c r="B558" t="inlineStr"/>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr"/>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t xml:space="preserve">patiemur persaepe </t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr"/>
+      <c r="B559" t="inlineStr"/>
+      <c r="C559" t="inlineStr"/>
+      <c r="D559" t="inlineStr"/>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poeta perpauca </t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr"/>
+      <c r="C560" t="inlineStr"/>
+      <c r="D560" t="inlineStr"/>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>The following words are stressed on the penult because their penults are long by position.Practice pronouncing them out loud,stressing the penult.</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr"/>
+      <c r="C561" t="inlineStr"/>
+      <c r="D561" t="inlineStr"/>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>以下单词重读倒数第二音节，因为它们的倒数第二音节是位置长。请大声练习</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr"/>
+      <c r="C562" t="inlineStr"/>
+      <c r="D562" t="inlineStr"/>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>（后面一句是废话，删了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr"/>
+      <c r="B563" t="inlineStr"/>
+      <c r="C563" t="inlineStr"/>
+      <c r="D563" t="inlineStr"/>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ocellis contactum </t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr"/>
+      <c r="B564" t="inlineStr"/>
+      <c r="C564" t="inlineStr"/>
+      <c r="D564" t="inlineStr"/>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>magister expressit</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr"/>
+      <c r="B565" t="inlineStr"/>
+      <c r="C565" t="inlineStr"/>
+      <c r="D565" t="inlineStr"/>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> intellegenda   adversos </t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr"/>
+      <c r="B566" t="inlineStr"/>
+      <c r="C566" t="inlineStr"/>
+      <c r="D566" t="inlineStr"/>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t xml:space="preserve">conferri deportant </t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr"/>
+      <c r="B567" t="inlineStr"/>
+      <c r="C567" t="inlineStr"/>
+      <c r="D567" t="inlineStr"/>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1.In words of more than two syllables,the number of syllables is not important for determining the syllable to be stressed.Only the length of the penult determines stress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr"/>
+      <c r="C568" t="inlineStr"/>
+      <c r="D568" t="inlineStr"/>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>1.两个音节以上的单词中，音节数量并不影响重读音节，只有倒数第二音节的长度才能影响。</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr"/>
+      <c r="B569" t="inlineStr"/>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr"/>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>2.The lengths of the syllables other than the penult are not important for determining stress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr"/>
+      <c r="C570" t="inlineStr"/>
+      <c r="D570" t="inlineStr"/>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>2.倒数第二音节以外的音节长度不影响重读音节。</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>【正文原文】</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr"/>
+      <c r="C571" t="inlineStr"/>
+      <c r="D571" t="inlineStr"/>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>The following words are stressed on the antepenult because their penults are short.Practice pronouncing them out loud,stressing the antepenult.</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>【正文译文】</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr"/>
+      <c r="C572" t="inlineStr"/>
+      <c r="D572" t="inlineStr"/>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>以下单词重读倒数第三音节，因为它们的倒数第三音节是短音节，请大声练习。（后面一句是废话，删了）</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr"/>
+      <c r="B573" t="inlineStr"/>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>【译者：Lanx】</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr"/>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t xml:space="preserve">scientia tempora </t>
         </is>
       </c>
     </row>
